--- a/filer_2/10290511_linde_gas_a_s.xlsx
+++ b/filer_2/10290511_linde_gas_a_s.xlsx
@@ -5862,20 +5862,20 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>SUM(B5:B6)</f>
+        <f>IF(COUNT('res_raw_10290511'!$F$2,'res_raw_10290511'!$F$3)=0,'res_raw_10290511'!$F$4,SUM(B5:B6))</f>
         <v/>
       </c>
       <c r="C7" s="27">
-        <f>SUM(C5:C6)</f>
+        <f>IF(COUNT('res_raw_10290511'!$E$2,'res_raw_10290511'!$E$3)=0,'res_raw_10290511'!$E$4,SUM(C5:C6))</f>
         <v/>
       </c>
       <c r="D7" s="27">
-        <f>SUM(D5:D6)</f>
+        <f>IF(COUNT('res_raw_10290511'!$D$2,'res_raw_10290511'!$D$3)=0,'res_raw_10290511'!$D$4,SUM(D5:D6))</f>
         <v/>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning − Produktionsomkostninger. Matcher fsa:GrossResult.</t>
+          <t>Beregnet: Nettoomsætning − Produktionsomkostninger. Matcher fsa:GrossResult. Er komponenterne ikke indberettet, vises rapporteret fsa:GrossResult direkte.</t>
         </is>
       </c>
     </row>

--- a/filer_2/10290511_linde_gas_a_s.xlsx
+++ b/filer_2/10290511_linde_gas_a_s.xlsx
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,6 +233,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -628,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -853,49 +857,49 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Salgs- og distributionsomkostninger</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
         <f>'res_raw_10290511'!$B$5</f>
         <v/>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <f>'res_raw_10290511'!$C$5</f>
         <v/>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
         <f>'res_raw_10290511'!$D$5</f>
         <v/>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <f>'res_raw_10290511'!$E$5</f>
         <v/>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <f>'res_raw_10290511'!$F$5</f>
         <v/>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" s="9">
+      <c r="H7" s="12">
         <f>IFERROR(B7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="12">
         <f>IFERROR(C7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="12">
         <f>IFERROR(D7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="12">
         <f>IFERROR(E7/$B$7*100,"")</f>
         <v/>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="12">
         <f>IFERROR(F7/$B$7*100,"")</f>
         <v/>
       </c>
@@ -903,7 +907,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Administrationsomkostninger</t>
+          <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
       <c r="B8" s="8">
@@ -949,49 +953,49 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Andre driftsindtægter</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Administrationsomkostninger</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
         <f>'res_raw_10290511'!$B$7</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <f>'res_raw_10290511'!$C$7</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <f>'res_raw_10290511'!$D$7</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <f>'res_raw_10290511'!$E$7</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <f>'res_raw_10290511'!$F$7</f>
         <v/>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" s="12">
+      <c r="H9" s="9">
         <f>IFERROR(B9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="9">
         <f>IFERROR(C9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="9">
         <f>IFERROR(D9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="9">
         <f>IFERROR(E9/$B$9*100,"")</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="9">
         <f>IFERROR(F9/$B$9*100,"")</f>
         <v/>
       </c>
@@ -999,7 +1003,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Andre driftsomkostninger</t>
+          <t>Andre driftsindtægter</t>
         </is>
       </c>
       <c r="B10" s="5">
@@ -1045,97 +1049,97 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Andre driftsomkostninger</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>'res_raw_10290511'!$B$9</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>'res_raw_10290511'!$C$9</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>'res_raw_10290511'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>'res_raw_10290511'!$E$9</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>'res_raw_10290511'!$F$9</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="12">
+        <f>IFERROR(B11/$B$11*100,"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="12">
+        <f>IFERROR(C11/$B$11*100,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>IFERROR(D11/$B$11*100,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="12">
+        <f>IFERROR(E11/$B$11*100,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>IFERROR(F11/$B$11*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="8">
-        <f>'res_raw_10290511'!$B$9</f>
-        <v/>
-      </c>
-      <c r="C11" s="8">
-        <f>'res_raw_10290511'!$C$9</f>
-        <v/>
-      </c>
-      <c r="D11" s="8">
-        <f>'res_raw_10290511'!$D$9</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>'res_raw_10290511'!$E$9</f>
-        <v/>
-      </c>
-      <c r="F11" s="8">
-        <f>'res_raw_10290511'!$F$9</f>
-        <v/>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="9">
-        <f>IFERROR(B11/$B$11*100,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="9">
-        <f>IFERROR(C11/$B$11*100,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>IFERROR(D11/$B$11*100,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>IFERROR(E11/$B$11*100,"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>IFERROR(F11/$B$11*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Indtægter af kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
+      <c r="B12" s="8">
         <f>'res_raw_10290511'!$B$10</f>
         <v/>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="8">
         <f>'res_raw_10290511'!$C$10</f>
         <v/>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="8">
         <f>'res_raw_10290511'!$D$10</f>
         <v/>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="8">
         <f>'res_raw_10290511'!$E$10</f>
         <v/>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="8">
         <f>'res_raw_10290511'!$F$10</f>
         <v/>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="6">
+      <c r="H12" s="9">
         <f>IFERROR(B12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="9">
         <f>IFERROR(C12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="9">
         <f>IFERROR(D12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="9">
         <f>IFERROR(E12/$B$12*100,"")</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="9">
         <f>IFERROR(F12/$B$12*100,"")</f>
         <v/>
       </c>
@@ -1143,7 +1147,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Finansielle indtægter</t>
+          <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -1191,7 +1195,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Finansielle omkostninger</t>
+          <t>Finansielle indtægter</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -1237,49 +1241,49 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Finansielle poster, netto</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Finansielle omkostninger</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
         <f>'res_raw_10290511'!$B$13</f>
         <v/>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <f>'res_raw_10290511'!$C$13</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <f>'res_raw_10290511'!$D$13</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="11">
         <f>'res_raw_10290511'!$E$13</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="11">
         <f>'res_raw_10290511'!$F$13</f>
         <v/>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="9">
+      <c r="H15" s="12">
         <f>IFERROR(B15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="12">
         <f>IFERROR(C15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="12">
         <f>IFERROR(D15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="12">
         <f>IFERROR(E15/$B$15*100,"")</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="12">
         <f>IFERROR(F15/$B$15*100,"")</f>
         <v/>
       </c>
@@ -1287,7 +1291,7 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Resultat før skat</t>
+          <t>Finansielle poster, netto</t>
         </is>
       </c>
       <c r="B16" s="8">
@@ -1333,211 +1337,211 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Resultat før skat</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>'res_raw_10290511'!$B$15</f>
+        <v/>
+      </c>
+      <c r="C17" s="8">
+        <f>'res_raw_10290511'!$C$15</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>'res_raw_10290511'!$D$15</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>'res_raw_10290511'!$E$15</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>'res_raw_10290511'!$F$15</f>
+        <v/>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="9">
+        <f>IFERROR(B17/$B$17*100,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>IFERROR(C17/$B$17*100,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>IFERROR(D17/$B$17*100,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="9">
+        <f>IFERROR(E17/$B$17*100,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="9">
+        <f>IFERROR(F17/$B$17*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="11">
-        <f>'res_raw_10290511'!$B$15</f>
-        <v/>
-      </c>
-      <c r="C17" s="11">
-        <f>'res_raw_10290511'!$C$15</f>
-        <v/>
-      </c>
-      <c r="D17" s="11">
-        <f>'res_raw_10290511'!$D$15</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>'res_raw_10290511'!$E$15</f>
-        <v/>
-      </c>
-      <c r="F17" s="11">
-        <f>'res_raw_10290511'!$F$15</f>
-        <v/>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" s="12">
-        <f>IFERROR(B17/$B$17*100,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IFERROR(C17/$B$17*100,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="12">
-        <f>IFERROR(D17/$B$17*100,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>IFERROR(E17/$B$17*100,"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IFERROR(F17/$B$17*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="B18" s="5">
+        <f>'res_raw_10290511'!$B$16</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>'res_raw_10290511'!$C$16</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>'res_raw_10290511'!$D$16</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>'res_raw_10290511'!$E$16</f>
+        <v/>
+      </c>
+      <c r="F18" s="5">
+        <f>'res_raw_10290511'!$F$16</f>
+        <v/>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="6">
+        <f>IFERROR(B18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="6">
+        <f>IFERROR(C18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="6">
+        <f>IFERROR(D18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="6">
+        <f>IFERROR(E18/$B$18*100,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="6">
+        <f>IFERROR(F18/$B$18*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="8">
-        <f>'res_raw_10290511'!$B$16</f>
-        <v/>
-      </c>
-      <c r="C18" s="8">
-        <f>'res_raw_10290511'!$C$16</f>
-        <v/>
-      </c>
-      <c r="D18" s="8">
-        <f>'res_raw_10290511'!$D$16</f>
-        <v/>
-      </c>
-      <c r="E18" s="8">
-        <f>'res_raw_10290511'!$E$16</f>
-        <v/>
-      </c>
-      <c r="F18" s="8">
-        <f>'res_raw_10290511'!$F$16</f>
-        <v/>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="9">
-        <f>IFERROR(B18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
-        <f>IFERROR(C18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="9">
-        <f>IFERROR(D18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="9">
-        <f>IFERROR(E18/$B$18*100,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="9">
-        <f>IFERROR(F18/$B$18*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B19" s="8">
+        <f>'res_raw_10290511'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C19" s="8">
+        <f>'res_raw_10290511'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>'res_raw_10290511'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>'res_raw_10290511'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F19" s="8">
+        <f>'res_raw_10290511'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="9">
+        <f>IFERROR(B19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>IFERROR(C19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="9">
+        <f>IFERROR(D19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="9">
+        <f>IFERROR(E19/$B$19*100,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="9">
+        <f>IFERROR(F19/$B$19*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>AKTIVER t.kr.</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C21" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K21" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Grunde og bygninger</t>
-        </is>
-      </c>
-      <c r="B21" s="11">
-        <f>'balance_raw_10290511'!$B$2</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>'balance_raw_10290511'!$C$2</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
-        <f>'balance_raw_10290511'!$D$2</f>
-        <v/>
-      </c>
-      <c r="E21" s="11">
-        <f>'balance_raw_10290511'!$E$2</f>
-        <v/>
-      </c>
-      <c r="F21" s="11">
-        <f>'balance_raw_10290511'!$F$2</f>
-        <v/>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="12">
-        <f>IFERROR(B21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>IFERROR(C21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="12">
-        <f>IFERROR(D21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="12">
-        <f>IFERROR(E21/$B$21*100,"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="12">
-        <f>IFERROR(F21/$B$21*100,"")</f>
-        <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Produktionsanlæg og maskiner</t>
+          <t>Grunde og bygninger</t>
         </is>
       </c>
       <c r="B22" s="5">
-        <f>'balance_raw_10290511'!$B$3</f>
+        <f>'balance_raw_10290511'!$B$2</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>'balance_raw_10290511'!$C$3</f>
+        <f>'balance_raw_10290511'!$C$2</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>'balance_raw_10290511'!$D$3</f>
+        <f>'balance_raw_10290511'!$D$2</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>'balance_raw_10290511'!$E$3</f>
+        <f>'balance_raw_10290511'!$E$2</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>'balance_raw_10290511'!$F$3</f>
+        <f>'balance_raw_10290511'!$F$2</f>
         <v/>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1565,27 +1569,27 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Driftsmateriel og inventar</t>
+          <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
       <c r="B23" s="11">
-        <f>'balance_raw_10290511'!$B$4</f>
+        <f>'balance_raw_10290511'!$B$3</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>'balance_raw_10290511'!$C$4</f>
+        <f>'balance_raw_10290511'!$C$3</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>'balance_raw_10290511'!$D$4</f>
+        <f>'balance_raw_10290511'!$D$3</f>
         <v/>
       </c>
       <c r="E23" s="11">
-        <f>'balance_raw_10290511'!$E$4</f>
+        <f>'balance_raw_10290511'!$E$3</f>
         <v/>
       </c>
       <c r="F23" s="11">
-        <f>'balance_raw_10290511'!$F$4</f>
+        <f>'balance_raw_10290511'!$F$3</f>
         <v/>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1613,27 +1617,27 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Indretning af lejede lokaler</t>
+          <t>Driftsmateriel og inventar</t>
         </is>
       </c>
       <c r="B24" s="5">
-        <f>'balance_raw_10290511'!$B$5</f>
+        <f>'balance_raw_10290511'!$B$4</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>'balance_raw_10290511'!$C$5</f>
+        <f>'balance_raw_10290511'!$C$4</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>'balance_raw_10290511'!$D$5</f>
+        <f>'balance_raw_10290511'!$D$4</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>'balance_raw_10290511'!$E$5</f>
+        <f>'balance_raw_10290511'!$E$4</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>'balance_raw_10290511'!$F$5</f>
+        <f>'balance_raw_10290511'!$F$4</f>
         <v/>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1661,27 +1665,27 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+          <t>Indretning af lejede lokaler</t>
         </is>
       </c>
       <c r="B25" s="11">
-        <f>'balance_raw_10290511'!$B$6</f>
+        <f>'balance_raw_10290511'!$B$5</f>
         <v/>
       </c>
       <c r="C25" s="11">
-        <f>'balance_raw_10290511'!$C$6</f>
+        <f>'balance_raw_10290511'!$C$5</f>
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>'balance_raw_10290511'!$D$6</f>
+        <f>'balance_raw_10290511'!$D$5</f>
         <v/>
       </c>
       <c r="E25" s="11">
-        <f>'balance_raw_10290511'!$E$6</f>
+        <f>'balance_raw_10290511'!$E$5</f>
         <v/>
       </c>
       <c r="F25" s="11">
-        <f>'balance_raw_10290511'!$F$6</f>
+        <f>'balance_raw_10290511'!$F$5</f>
         <v/>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1707,97 +1711,97 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+        </is>
+      </c>
+      <c r="B26" s="5">
+        <f>'balance_raw_10290511'!$B$6</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>'balance_raw_10290511'!$C$6</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>'balance_raw_10290511'!$D$6</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>'balance_raw_10290511'!$E$6</f>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>'balance_raw_10290511'!$F$6</f>
+        <v/>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="6">
+        <f>IFERROR(B26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="6">
+        <f>IFERROR(C26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="6">
+        <f>IFERROR(D26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="6">
+        <f>IFERROR(E26/$B$26*100,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="6">
+        <f>IFERROR(F26/$B$26*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B26" s="8">
+      <c r="B27" s="8">
         <f>'balance_raw_10290511'!$B$7</f>
         <v/>
       </c>
-      <c r="C26" s="8">
+      <c r="C27" s="8">
         <f>'balance_raw_10290511'!$C$7</f>
         <v/>
       </c>
-      <c r="D26" s="8">
+      <c r="D27" s="8">
         <f>'balance_raw_10290511'!$D$7</f>
         <v/>
       </c>
-      <c r="E26" s="8">
+      <c r="E27" s="8">
         <f>'balance_raw_10290511'!$E$7</f>
         <v/>
       </c>
-      <c r="F26" s="8">
+      <c r="F27" s="8">
         <f>'balance_raw_10290511'!$F$7</f>
         <v/>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="9">
-        <f>IFERROR(B26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="9">
-        <f>IFERROR(C26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="9">
-        <f>IFERROR(D26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="9">
-        <f>IFERROR(E26/$B$26*100,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="9">
-        <f>IFERROR(F26/$B$26*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>Kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B27" s="11">
-        <f>'balance_raw_10290511'!$B$8</f>
-        <v/>
-      </c>
-      <c r="C27" s="11">
-        <f>'balance_raw_10290511'!$C$8</f>
-        <v/>
-      </c>
-      <c r="D27" s="11">
-        <f>'balance_raw_10290511'!$D$8</f>
-        <v/>
-      </c>
-      <c r="E27" s="11">
-        <f>'balance_raw_10290511'!$E$8</f>
-        <v/>
-      </c>
-      <c r="F27" s="11">
-        <f>'balance_raw_10290511'!$F$8</f>
-        <v/>
-      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" s="12">
+      <c r="H27" s="9">
         <f>IFERROR(B27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="9">
         <f>IFERROR(C27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="9">
         <f>IFERROR(D27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="9">
         <f>IFERROR(E27/$B$27*100,"")</f>
         <v/>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="9">
         <f>IFERROR(F27/$B$27*100,"")</f>
         <v/>
       </c>
@@ -1805,27 +1809,27 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Deposita</t>
+          <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <f>'balance_raw_10290511'!$B$9</f>
+        <f>'balance_raw_10290511'!$B$8</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>'balance_raw_10290511'!$C$9</f>
+        <f>'balance_raw_10290511'!$C$8</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>'balance_raw_10290511'!$D$9</f>
+        <f>'balance_raw_10290511'!$D$8</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>'balance_raw_10290511'!$E$9</f>
+        <f>'balance_raw_10290511'!$E$8</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>'balance_raw_10290511'!$F$9</f>
+        <f>'balance_raw_10290511'!$F$8</f>
         <v/>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1851,49 +1855,49 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B29" s="8">
-        <f>'balance_raw_10290511'!$B$10</f>
-        <v/>
-      </c>
-      <c r="C29" s="8">
-        <f>'balance_raw_10290511'!$C$10</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>'balance_raw_10290511'!$D$10</f>
-        <v/>
-      </c>
-      <c r="E29" s="8">
-        <f>'balance_raw_10290511'!$E$10</f>
-        <v/>
-      </c>
-      <c r="F29" s="8">
-        <f>'balance_raw_10290511'!$F$10</f>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Deposita</t>
+        </is>
+      </c>
+      <c r="B29" s="11">
+        <f>'balance_raw_10290511'!$B$9</f>
+        <v/>
+      </c>
+      <c r="C29" s="11">
+        <f>'balance_raw_10290511'!$C$9</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>'balance_raw_10290511'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>'balance_raw_10290511'!$E$9</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>'balance_raw_10290511'!$F$9</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="12">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="12">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="12">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="12">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1901,27 +1905,27 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Anlægsaktiver</t>
+          <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B30" s="8">
-        <f>'balance_raw_10290511'!$B$11</f>
+        <f>'balance_raw_10290511'!$B$10</f>
         <v/>
       </c>
       <c r="C30" s="8">
-        <f>'balance_raw_10290511'!$C$11</f>
+        <f>'balance_raw_10290511'!$C$10</f>
         <v/>
       </c>
       <c r="D30" s="8">
-        <f>'balance_raw_10290511'!$D$11</f>
+        <f>'balance_raw_10290511'!$D$10</f>
         <v/>
       </c>
       <c r="E30" s="8">
-        <f>'balance_raw_10290511'!$E$11</f>
+        <f>'balance_raw_10290511'!$E$10</f>
         <v/>
       </c>
       <c r="F30" s="8">
-        <f>'balance_raw_10290511'!$F$11</f>
+        <f>'balance_raw_10290511'!$F$10</f>
         <v/>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1947,49 +1951,49 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B31" s="11">
-        <f>'balance_raw_10290511'!$B$12</f>
-        <v/>
-      </c>
-      <c r="C31" s="11">
-        <f>'balance_raw_10290511'!$C$12</f>
-        <v/>
-      </c>
-      <c r="D31" s="11">
-        <f>'balance_raw_10290511'!$D$12</f>
-        <v/>
-      </c>
-      <c r="E31" s="11">
-        <f>'balance_raw_10290511'!$E$12</f>
-        <v/>
-      </c>
-      <c r="F31" s="11">
-        <f>'balance_raw_10290511'!$F$12</f>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="8">
+        <f>'balance_raw_10290511'!$B$11</f>
+        <v/>
+      </c>
+      <c r="C31" s="8">
+        <f>'balance_raw_10290511'!$C$11</f>
+        <v/>
+      </c>
+      <c r="D31" s="8">
+        <f>'balance_raw_10290511'!$D$11</f>
+        <v/>
+      </c>
+      <c r="E31" s="8">
+        <f>'balance_raw_10290511'!$E$11</f>
+        <v/>
+      </c>
+      <c r="F31" s="8">
+        <f>'balance_raw_10290511'!$F$11</f>
         <v/>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" s="12">
+      <c r="H31" s="9">
         <f>IFERROR(B31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="9">
         <f>IFERROR(C31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="9">
         <f>IFERROR(D31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="9">
         <f>IFERROR(E31/$B$31*100,"")</f>
         <v/>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="9">
         <f>IFERROR(F31/$B$31*100,"")</f>
         <v/>
       </c>
@@ -1997,27 +2001,27 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Varer under fremstilling</t>
+          <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <f>'balance_raw_10290511'!$B$13</f>
+        <f>'balance_raw_10290511'!$B$12</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>'balance_raw_10290511'!$C$13</f>
+        <f>'balance_raw_10290511'!$C$12</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>'balance_raw_10290511'!$D$13</f>
+        <f>'balance_raw_10290511'!$D$12</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>'balance_raw_10290511'!$E$13</f>
+        <f>'balance_raw_10290511'!$E$12</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>'balance_raw_10290511'!$F$13</f>
+        <f>'balance_raw_10290511'!$F$12</f>
         <v/>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -2045,27 +2049,27 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Færdigvarer og handelsvarer</t>
+          <t>Varer under fremstilling</t>
         </is>
       </c>
       <c r="B33" s="11">
-        <f>'balance_raw_10290511'!$B$14</f>
+        <f>'balance_raw_10290511'!$B$13</f>
         <v/>
       </c>
       <c r="C33" s="11">
-        <f>'balance_raw_10290511'!$C$14</f>
+        <f>'balance_raw_10290511'!$C$13</f>
         <v/>
       </c>
       <c r="D33" s="11">
-        <f>'balance_raw_10290511'!$D$14</f>
+        <f>'balance_raw_10290511'!$D$13</f>
         <v/>
       </c>
       <c r="E33" s="11">
-        <f>'balance_raw_10290511'!$E$14</f>
+        <f>'balance_raw_10290511'!$E$13</f>
         <v/>
       </c>
       <c r="F33" s="11">
-        <f>'balance_raw_10290511'!$F$14</f>
+        <f>'balance_raw_10290511'!$F$13</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2091,97 +2095,97 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Færdigvarer og handelsvarer</t>
+        </is>
+      </c>
+      <c r="B34" s="5">
+        <f>'balance_raw_10290511'!$B$14</f>
+        <v/>
+      </c>
+      <c r="C34" s="5">
+        <f>'balance_raw_10290511'!$C$14</f>
+        <v/>
+      </c>
+      <c r="D34" s="5">
+        <f>'balance_raw_10290511'!$D$14</f>
+        <v/>
+      </c>
+      <c r="E34" s="5">
+        <f>'balance_raw_10290511'!$E$14</f>
+        <v/>
+      </c>
+      <c r="F34" s="5">
+        <f>'balance_raw_10290511'!$F$14</f>
+        <v/>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="6">
+        <f>IFERROR(B34/$B$34*100,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="6">
+        <f>IFERROR(C34/$B$34*100,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="6">
+        <f>IFERROR(D34/$B$34*100,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="6">
+        <f>IFERROR(E34/$B$34*100,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IFERROR(F34/$B$34*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B34" s="8">
+      <c r="B35" s="8">
         <f>'balance_raw_10290511'!$B$15</f>
         <v/>
       </c>
-      <c r="C34" s="8">
+      <c r="C35" s="8">
         <f>'balance_raw_10290511'!$C$15</f>
         <v/>
       </c>
-      <c r="D34" s="8">
+      <c r="D35" s="8">
         <f>'balance_raw_10290511'!$D$15</f>
         <v/>
       </c>
-      <c r="E34" s="8">
+      <c r="E35" s="8">
         <f>'balance_raw_10290511'!$E$15</f>
         <v/>
       </c>
-      <c r="F34" s="8">
+      <c r="F35" s="8">
         <f>'balance_raw_10290511'!$F$15</f>
         <v/>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" s="9">
-        <f>IFERROR(B34/$B$34*100,"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="9">
-        <f>IFERROR(C34/$B$34*100,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="9">
-        <f>IFERROR(D34/$B$34*100,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="9">
-        <f>IFERROR(E34/$B$34*100,"")</f>
-        <v/>
-      </c>
-      <c r="L34" s="9">
-        <f>IFERROR(F34/$B$34*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B35" s="11">
-        <f>'balance_raw_10290511'!$B$16</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>'balance_raw_10290511'!$C$16</f>
-        <v/>
-      </c>
-      <c r="D35" s="11">
-        <f>'balance_raw_10290511'!$D$16</f>
-        <v/>
-      </c>
-      <c r="E35" s="11">
-        <f>'balance_raw_10290511'!$E$16</f>
-        <v/>
-      </c>
-      <c r="F35" s="11">
-        <f>'balance_raw_10290511'!$F$16</f>
-        <v/>
-      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="12">
+      <c r="H35" s="9">
         <f>IFERROR(B35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="9">
         <f>IFERROR(C35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="J35" s="12">
+      <c r="J35" s="9">
         <f>IFERROR(D35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="9">
         <f>IFERROR(E35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="L35" s="12">
+      <c r="L35" s="9">
         <f>IFERROR(F35/$B$35*100,"")</f>
         <v/>
       </c>
@@ -2189,27 +2193,27 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B36" s="5">
-        <f>'balance_raw_10290511'!$B$17</f>
+        <f>'balance_raw_10290511'!$B$16</f>
         <v/>
       </c>
       <c r="C36" s="5">
-        <f>'balance_raw_10290511'!$C$17</f>
+        <f>'balance_raw_10290511'!$C$16</f>
         <v/>
       </c>
       <c r="D36" s="5">
-        <f>'balance_raw_10290511'!$D$17</f>
+        <f>'balance_raw_10290511'!$D$16</f>
         <v/>
       </c>
       <c r="E36" s="5">
-        <f>'balance_raw_10290511'!$E$17</f>
+        <f>'balance_raw_10290511'!$E$16</f>
         <v/>
       </c>
       <c r="F36" s="5">
-        <f>'balance_raw_10290511'!$F$17</f>
+        <f>'balance_raw_10290511'!$F$16</f>
         <v/>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2237,27 +2241,27 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Andre tilgodehavender</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B37" s="11">
-        <f>'balance_raw_10290511'!$B$18</f>
+        <f>'balance_raw_10290511'!$B$17</f>
         <v/>
       </c>
       <c r="C37" s="11">
-        <f>'balance_raw_10290511'!$C$18</f>
+        <f>'balance_raw_10290511'!$C$17</f>
         <v/>
       </c>
       <c r="D37" s="11">
-        <f>'balance_raw_10290511'!$D$18</f>
+        <f>'balance_raw_10290511'!$D$17</f>
         <v/>
       </c>
       <c r="E37" s="11">
-        <f>'balance_raw_10290511'!$E$18</f>
+        <f>'balance_raw_10290511'!$E$17</f>
         <v/>
       </c>
       <c r="F37" s="11">
-        <f>'balance_raw_10290511'!$F$18</f>
+        <f>'balance_raw_10290511'!$F$17</f>
         <v/>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2285,27 +2289,27 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <f>'balance_raw_10290511'!$B$19</f>
+        <f>'balance_raw_10290511'!$B$18</f>
         <v/>
       </c>
       <c r="C38" s="5">
-        <f>'balance_raw_10290511'!$C$19</f>
+        <f>'balance_raw_10290511'!$C$18</f>
         <v/>
       </c>
       <c r="D38" s="5">
-        <f>'balance_raw_10290511'!$D$19</f>
+        <f>'balance_raw_10290511'!$D$18</f>
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>'balance_raw_10290511'!$E$19</f>
+        <f>'balance_raw_10290511'!$E$18</f>
         <v/>
       </c>
       <c r="F38" s="5">
-        <f>'balance_raw_10290511'!$F$19</f>
+        <f>'balance_raw_10290511'!$F$18</f>
         <v/>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2333,27 +2337,27 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B39" s="11">
-        <f>'balance_raw_10290511'!$B$20</f>
+        <f>'balance_raw_10290511'!$B$19</f>
         <v/>
       </c>
       <c r="C39" s="11">
-        <f>'balance_raw_10290511'!$C$20</f>
+        <f>'balance_raw_10290511'!$C$19</f>
         <v/>
       </c>
       <c r="D39" s="11">
-        <f>'balance_raw_10290511'!$D$20</f>
+        <f>'balance_raw_10290511'!$D$19</f>
         <v/>
       </c>
       <c r="E39" s="11">
-        <f>'balance_raw_10290511'!$E$20</f>
+        <f>'balance_raw_10290511'!$E$19</f>
         <v/>
       </c>
       <c r="F39" s="11">
-        <f>'balance_raw_10290511'!$F$20</f>
+        <f>'balance_raw_10290511'!$F$19</f>
         <v/>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2381,27 +2385,27 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Udskudt skatteaktiv</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <f>'balance_raw_10290511'!$B$21</f>
+        <f>'balance_raw_10290511'!$B$20</f>
         <v/>
       </c>
       <c r="C40" s="5">
-        <f>'balance_raw_10290511'!$C$21</f>
+        <f>'balance_raw_10290511'!$C$20</f>
         <v/>
       </c>
       <c r="D40" s="5">
-        <f>'balance_raw_10290511'!$D$21</f>
+        <f>'balance_raw_10290511'!$D$20</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>'balance_raw_10290511'!$E$21</f>
+        <f>'balance_raw_10290511'!$E$20</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>'balance_raw_10290511'!$F$21</f>
+        <f>'balance_raw_10290511'!$F$20</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2429,27 +2433,27 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B41" s="11">
-        <f>'balance_raw_10290511'!$B$22</f>
+        <f>'balance_raw_10290511'!$B$21</f>
         <v/>
       </c>
       <c r="C41" s="11">
-        <f>'balance_raw_10290511'!$C$22</f>
+        <f>'balance_raw_10290511'!$C$21</f>
         <v/>
       </c>
       <c r="D41" s="11">
-        <f>'balance_raw_10290511'!$D$22</f>
+        <f>'balance_raw_10290511'!$D$21</f>
         <v/>
       </c>
       <c r="E41" s="11">
-        <f>'balance_raw_10290511'!$E$22</f>
+        <f>'balance_raw_10290511'!$E$21</f>
         <v/>
       </c>
       <c r="F41" s="11">
-        <f>'balance_raw_10290511'!$F$22</f>
+        <f>'balance_raw_10290511'!$F$21</f>
         <v/>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2475,97 +2479,97 @@
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B42" s="5">
+        <f>'balance_raw_10290511'!$B$22</f>
+        <v/>
+      </c>
+      <c r="C42" s="5">
+        <f>'balance_raw_10290511'!$C$22</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>'balance_raw_10290511'!$D$22</f>
+        <v/>
+      </c>
+      <c r="E42" s="5">
+        <f>'balance_raw_10290511'!$E$22</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>'balance_raw_10290511'!$F$22</f>
+        <v/>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" s="6">
+        <f>IFERROR(B42/$B$42*100,"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="6">
+        <f>IFERROR(C42/$B$42*100,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="6">
+        <f>IFERROR(D42/$B$42*100,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="6">
+        <f>IFERROR(E42/$B$42*100,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="6">
+        <f>IFERROR(F42/$B$42*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B42" s="8">
+      <c r="B43" s="8">
         <f>'balance_raw_10290511'!$B$23</f>
         <v/>
       </c>
-      <c r="C42" s="8">
+      <c r="C43" s="8">
         <f>'balance_raw_10290511'!$C$23</f>
         <v/>
       </c>
-      <c r="D42" s="8">
+      <c r="D43" s="8">
         <f>'balance_raw_10290511'!$D$23</f>
         <v/>
       </c>
-      <c r="E42" s="8">
+      <c r="E43" s="8">
         <f>'balance_raw_10290511'!$E$23</f>
         <v/>
       </c>
-      <c r="F42" s="8">
+      <c r="F43" s="8">
         <f>'balance_raw_10290511'!$F$23</f>
         <v/>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="9">
-        <f>IFERROR(B42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="9">
-        <f>IFERROR(C42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="9">
-        <f>IFERROR(D42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="9">
-        <f>IFERROR(E42/$B$42*100,"")</f>
-        <v/>
-      </c>
-      <c r="L42" s="9">
-        <f>IFERROR(F42/$B$42*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
-        <f>'balance_raw_10290511'!$B$24</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>'balance_raw_10290511'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>'balance_raw_10290511'!$D$24</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>'balance_raw_10290511'!$E$24</f>
-        <v/>
-      </c>
-      <c r="F43" s="11">
-        <f>'balance_raw_10290511'!$F$24</f>
-        <v/>
-      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" s="12">
+      <c r="H43" s="9">
         <f>IFERROR(B43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="9">
         <f>IFERROR(C43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="9">
         <f>IFERROR(D43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="9">
         <f>IFERROR(E43/$B$43*100,"")</f>
         <v/>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="9">
         <f>IFERROR(F43/$B$43*100,"")</f>
         <v/>
       </c>
@@ -2573,27 +2577,27 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Værdipapirer</t>
         </is>
       </c>
       <c r="B44" s="5">
-        <f>'balance_raw_10290511'!$B$25</f>
+        <f>'balance_raw_10290511'!$B$24</f>
         <v/>
       </c>
       <c r="C44" s="5">
-        <f>'balance_raw_10290511'!$C$25</f>
+        <f>'balance_raw_10290511'!$C$24</f>
         <v/>
       </c>
       <c r="D44" s="5">
-        <f>'balance_raw_10290511'!$D$25</f>
+        <f>'balance_raw_10290511'!$D$24</f>
         <v/>
       </c>
       <c r="E44" s="5">
-        <f>'balance_raw_10290511'!$E$25</f>
+        <f>'balance_raw_10290511'!$E$24</f>
         <v/>
       </c>
       <c r="F44" s="5">
-        <f>'balance_raw_10290511'!$F$25</f>
+        <f>'balance_raw_10290511'!$F$24</f>
         <v/>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2619,49 +2623,49 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>'balance_raw_10290511'!$B$26</f>
-        <v/>
-      </c>
-      <c r="C45" s="8">
-        <f>'balance_raw_10290511'!$C$26</f>
-        <v/>
-      </c>
-      <c r="D45" s="8">
-        <f>'balance_raw_10290511'!$D$26</f>
-        <v/>
-      </c>
-      <c r="E45" s="8">
-        <f>'balance_raw_10290511'!$E$26</f>
-        <v/>
-      </c>
-      <c r="F45" s="8">
-        <f>'balance_raw_10290511'!$F$26</f>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B45" s="11">
+        <f>'balance_raw_10290511'!$B$25</f>
+        <v/>
+      </c>
+      <c r="C45" s="11">
+        <f>'balance_raw_10290511'!$C$25</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>'balance_raw_10290511'!$D$25</f>
+        <v/>
+      </c>
+      <c r="E45" s="11">
+        <f>'balance_raw_10290511'!$E$25</f>
+        <v/>
+      </c>
+      <c r="F45" s="11">
+        <f>'balance_raw_10290511'!$F$25</f>
         <v/>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="9">
+      <c r="H45" s="12">
         <f>IFERROR(B45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="12">
         <f>IFERROR(C45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="12">
         <f>IFERROR(D45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="12">
         <f>IFERROR(E45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="12">
         <f>IFERROR(F45/$B$45*100,"")</f>
         <v/>
       </c>
@@ -2669,27 +2673,27 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Aktiver</t>
+          <t>Omsætningsaktiver</t>
         </is>
       </c>
       <c r="B46" s="8">
-        <f>'balance_raw_10290511'!$B$27</f>
+        <f>'balance_raw_10290511'!$B$26</f>
         <v/>
       </c>
       <c r="C46" s="8">
-        <f>'balance_raw_10290511'!$C$27</f>
+        <f>'balance_raw_10290511'!$C$26</f>
         <v/>
       </c>
       <c r="D46" s="8">
-        <f>'balance_raw_10290511'!$D$27</f>
+        <f>'balance_raw_10290511'!$D$26</f>
         <v/>
       </c>
       <c r="E46" s="8">
-        <f>'balance_raw_10290511'!$E$27</f>
+        <f>'balance_raw_10290511'!$E$26</f>
         <v/>
       </c>
       <c r="F46" s="8">
-        <f>'balance_raw_10290511'!$F$27</f>
+        <f>'balance_raw_10290511'!$F$26</f>
         <v/>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2714,116 +2718,116 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B47" s="8">
+        <f>'balance_raw_10290511'!$B$27</f>
+        <v/>
+      </c>
+      <c r="C47" s="8">
+        <f>'balance_raw_10290511'!$C$27</f>
+        <v/>
+      </c>
+      <c r="D47" s="8">
+        <f>'balance_raw_10290511'!$D$27</f>
+        <v/>
+      </c>
+      <c r="E47" s="8">
+        <f>'balance_raw_10290511'!$E$27</f>
+        <v/>
+      </c>
+      <c r="F47" s="8">
+        <f>'balance_raw_10290511'!$F$27</f>
+        <v/>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" s="9">
+        <f>IFERROR(B47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="9">
+        <f>IFERROR(C47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="9">
+        <f>IFERROR(D47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="9">
+        <f>IFERROR(E47/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="9">
+        <f>IFERROR(F47/$B$47*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>PASSIVER t.kr.</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B49" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C49" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="3" t="n">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I49" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="J49" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="K49" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="L49" s="3" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B49" s="11">
-        <f>'balance_raw_10290511'!$B$28</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>'balance_raw_10290511'!$C$28</f>
-        <v/>
-      </c>
-      <c r="D49" s="11">
-        <f>'balance_raw_10290511'!$D$28</f>
-        <v/>
-      </c>
-      <c r="E49" s="11">
-        <f>'balance_raw_10290511'!$E$28</f>
-        <v/>
-      </c>
-      <c r="F49" s="11">
-        <f>'balance_raw_10290511'!$F$28</f>
-        <v/>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="12">
-        <f>IFERROR(B49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="12">
-        <f>IFERROR(C49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="12">
-        <f>IFERROR(D49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="12">
-        <f>IFERROR(E49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="12">
-        <f>IFERROR(F49/$B$49*100,"")</f>
-        <v/>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B50" s="5">
-        <f>'balance_raw_10290511'!$B$29</f>
+        <f>'balance_raw_10290511'!$B$28</f>
         <v/>
       </c>
       <c r="C50" s="5">
-        <f>'balance_raw_10290511'!$C$29</f>
+        <f>'balance_raw_10290511'!$C$28</f>
         <v/>
       </c>
       <c r="D50" s="5">
-        <f>'balance_raw_10290511'!$D$29</f>
+        <f>'balance_raw_10290511'!$D$28</f>
         <v/>
       </c>
       <c r="E50" s="5">
-        <f>'balance_raw_10290511'!$E$29</f>
+        <f>'balance_raw_10290511'!$E$28</f>
         <v/>
       </c>
       <c r="F50" s="5">
-        <f>'balance_raw_10290511'!$F$29</f>
+        <f>'balance_raw_10290511'!$F$28</f>
         <v/>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2851,27 +2855,27 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Reserve for udviklingsomkostninger</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B51" s="11">
-        <f>'balance_raw_10290511'!$B$30</f>
+        <f>'balance_raw_10290511'!$B$29</f>
         <v/>
       </c>
       <c r="C51" s="11">
-        <f>'balance_raw_10290511'!$C$30</f>
+        <f>'balance_raw_10290511'!$C$29</f>
         <v/>
       </c>
       <c r="D51" s="11">
-        <f>'balance_raw_10290511'!$D$30</f>
+        <f>'balance_raw_10290511'!$D$29</f>
         <v/>
       </c>
       <c r="E51" s="11">
-        <f>'balance_raw_10290511'!$E$30</f>
+        <f>'balance_raw_10290511'!$E$29</f>
         <v/>
       </c>
       <c r="F51" s="11">
-        <f>'balance_raw_10290511'!$F$30</f>
+        <f>'balance_raw_10290511'!$F$29</f>
         <v/>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2899,27 +2903,27 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B52" s="5">
-        <f>'balance_raw_10290511'!$B$31</f>
+        <f>'balance_raw_10290511'!$B$30</f>
         <v/>
       </c>
       <c r="C52" s="5">
-        <f>'balance_raw_10290511'!$C$31</f>
+        <f>'balance_raw_10290511'!$C$30</f>
         <v/>
       </c>
       <c r="D52" s="5">
-        <f>'balance_raw_10290511'!$D$31</f>
+        <f>'balance_raw_10290511'!$D$30</f>
         <v/>
       </c>
       <c r="E52" s="5">
-        <f>'balance_raw_10290511'!$E$31</f>
+        <f>'balance_raw_10290511'!$E$30</f>
         <v/>
       </c>
       <c r="F52" s="5">
-        <f>'balance_raw_10290511'!$F$31</f>
+        <f>'balance_raw_10290511'!$F$30</f>
         <v/>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2947,27 +2951,27 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
       <c r="B53" s="11">
-        <f>'balance_raw_10290511'!$B$32</f>
+        <f>'balance_raw_10290511'!$B$31</f>
         <v/>
       </c>
       <c r="C53" s="11">
-        <f>'balance_raw_10290511'!$C$32</f>
+        <f>'balance_raw_10290511'!$C$31</f>
         <v/>
       </c>
       <c r="D53" s="11">
-        <f>'balance_raw_10290511'!$D$32</f>
+        <f>'balance_raw_10290511'!$D$31</f>
         <v/>
       </c>
       <c r="E53" s="11">
-        <f>'balance_raw_10290511'!$E$32</f>
+        <f>'balance_raw_10290511'!$E$31</f>
         <v/>
       </c>
       <c r="F53" s="11">
-        <f>'balance_raw_10290511'!$F$32</f>
+        <f>'balance_raw_10290511'!$F$31</f>
         <v/>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2995,27 +2999,27 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B54" s="5">
-        <f>'balance_raw_10290511'!$B$33</f>
+        <f>'balance_raw_10290511'!$B$32</f>
         <v/>
       </c>
       <c r="C54" s="5">
-        <f>'balance_raw_10290511'!$C$33</f>
+        <f>'balance_raw_10290511'!$C$32</f>
         <v/>
       </c>
       <c r="D54" s="5">
-        <f>'balance_raw_10290511'!$D$33</f>
+        <f>'balance_raw_10290511'!$D$32</f>
         <v/>
       </c>
       <c r="E54" s="5">
-        <f>'balance_raw_10290511'!$E$33</f>
+        <f>'balance_raw_10290511'!$E$32</f>
         <v/>
       </c>
       <c r="F54" s="5">
-        <f>'balance_raw_10290511'!$F$33</f>
+        <f>'balance_raw_10290511'!$F$32</f>
         <v/>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3041,145 +3045,145 @@
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B55" s="11">
+        <f>'balance_raw_10290511'!$B$33</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>'balance_raw_10290511'!$C$33</f>
+        <v/>
+      </c>
+      <c r="D55" s="11">
+        <f>'balance_raw_10290511'!$D$33</f>
+        <v/>
+      </c>
+      <c r="E55" s="11">
+        <f>'balance_raw_10290511'!$E$33</f>
+        <v/>
+      </c>
+      <c r="F55" s="11">
+        <f>'balance_raw_10290511'!$F$33</f>
+        <v/>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" s="12">
+        <f>IFERROR(B55/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="12">
+        <f>IFERROR(C55/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="12">
+        <f>IFERROR(D55/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="K55" s="12">
+        <f>IFERROR(E55/$B$55*100,"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="12">
+        <f>IFERROR(F55/$B$55*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B55" s="8">
+      <c r="B56" s="8">
         <f>'balance_raw_10290511'!$B$34</f>
         <v/>
       </c>
-      <c r="C55" s="8">
+      <c r="C56" s="8">
         <f>'balance_raw_10290511'!$C$34</f>
         <v/>
       </c>
-      <c r="D55" s="8">
+      <c r="D56" s="8">
         <f>'balance_raw_10290511'!$D$34</f>
         <v/>
       </c>
-      <c r="E55" s="8">
+      <c r="E56" s="8">
         <f>'balance_raw_10290511'!$E$34</f>
         <v/>
       </c>
-      <c r="F55" s="8">
+      <c r="F56" s="8">
         <f>'balance_raw_10290511'!$F$34</f>
         <v/>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" s="9">
-        <f>IFERROR(B55/$B$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="9">
-        <f>IFERROR(C55/$B$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="9">
-        <f>IFERROR(D55/$B$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="9">
-        <f>IFERROR(E55/$B$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="L55" s="9">
-        <f>IFERROR(F55/$B$55*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" s="9">
+        <f>IFERROR(B56/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="9">
+        <f>IFERROR(C56/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="9">
+        <f>IFERROR(D56/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="K56" s="9">
+        <f>IFERROR(E56/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="9">
+        <f>IFERROR(F56/$B$56*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B56" s="5">
+      <c r="B57" s="11">
         <f>'balance_raw_10290511'!$B$35</f>
         <v/>
       </c>
-      <c r="C56" s="5">
+      <c r="C57" s="11">
         <f>'balance_raw_10290511'!$C$35</f>
         <v/>
       </c>
-      <c r="D56" s="5">
+      <c r="D57" s="11">
         <f>'balance_raw_10290511'!$D$35</f>
         <v/>
       </c>
-      <c r="E56" s="5">
+      <c r="E57" s="11">
         <f>'balance_raw_10290511'!$E$35</f>
         <v/>
       </c>
-      <c r="F56" s="5">
+      <c r="F57" s="11">
         <f>'balance_raw_10290511'!$F$35</f>
         <v/>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" s="6">
-        <f>IFERROR(B56/$B$56*100,"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>IFERROR(C56/$B$56*100,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>IFERROR(D56/$B$56*100,"")</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>IFERROR(E56/$B$56*100,"")</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>IFERROR(F56/$B$56*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>'balance_raw_10290511'!$B$36</f>
-        <v/>
-      </c>
-      <c r="C57" s="8">
-        <f>'balance_raw_10290511'!$C$36</f>
-        <v/>
-      </c>
-      <c r="D57" s="8">
-        <f>'balance_raw_10290511'!$D$36</f>
-        <v/>
-      </c>
-      <c r="E57" s="8">
-        <f>'balance_raw_10290511'!$E$36</f>
-        <v/>
-      </c>
-      <c r="F57" s="8">
-        <f>'balance_raw_10290511'!$F$36</f>
-        <v/>
-      </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" s="9">
+      <c r="H57" s="12">
         <f>IFERROR(B57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="12">
         <f>IFERROR(C57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="12">
         <f>IFERROR(D57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="12">
         <f>IFERROR(E57/$B$57*100,"")</f>
         <v/>
       </c>
-      <c r="L57" s="9">
+      <c r="L57" s="12">
         <f>IFERROR(F57/$B$57*100,"")</f>
         <v/>
       </c>
@@ -3187,27 +3191,27 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Langfristede gældsforpligtelser</t>
+          <t>Hensatte forpligtelser</t>
         </is>
       </c>
       <c r="B58" s="8">
-        <f>'balance_raw_10290511'!$B$37</f>
+        <f>'balance_raw_10290511'!$B$36</f>
         <v/>
       </c>
       <c r="C58" s="8">
-        <f>'balance_raw_10290511'!$C$37</f>
+        <f>'balance_raw_10290511'!$C$36</f>
         <v/>
       </c>
       <c r="D58" s="8">
-        <f>'balance_raw_10290511'!$D$37</f>
+        <f>'balance_raw_10290511'!$D$36</f>
         <v/>
       </c>
       <c r="E58" s="8">
-        <f>'balance_raw_10290511'!$E$37</f>
+        <f>'balance_raw_10290511'!$E$36</f>
         <v/>
       </c>
       <c r="F58" s="8">
-        <f>'balance_raw_10290511'!$F$37</f>
+        <f>'balance_raw_10290511'!$F$36</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3233,49 +3237,49 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B59" s="11">
-        <f>'balance_raw_10290511'!$B$38</f>
-        <v/>
-      </c>
-      <c r="C59" s="11">
-        <f>'balance_raw_10290511'!$C$38</f>
-        <v/>
-      </c>
-      <c r="D59" s="11">
-        <f>'balance_raw_10290511'!$D$38</f>
-        <v/>
-      </c>
-      <c r="E59" s="11">
-        <f>'balance_raw_10290511'!$E$38</f>
-        <v/>
-      </c>
-      <c r="F59" s="11">
-        <f>'balance_raw_10290511'!$F$38</f>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
+        <f>'balance_raw_10290511'!$B$37</f>
+        <v/>
+      </c>
+      <c r="C59" s="8">
+        <f>'balance_raw_10290511'!$C$37</f>
+        <v/>
+      </c>
+      <c r="D59" s="8">
+        <f>'balance_raw_10290511'!$D$37</f>
+        <v/>
+      </c>
+      <c r="E59" s="8">
+        <f>'balance_raw_10290511'!$E$37</f>
+        <v/>
+      </c>
+      <c r="F59" s="8">
+        <f>'balance_raw_10290511'!$F$37</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="12">
+      <c r="H59" s="9">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="12">
+      <c r="I59" s="9">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="9">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="9">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="9">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
@@ -3283,27 +3287,27 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B60" s="5">
-        <f>'balance_raw_10290511'!$B$39</f>
+        <f>'balance_raw_10290511'!$B$38</f>
         <v/>
       </c>
       <c r="C60" s="5">
-        <f>'balance_raw_10290511'!$C$39</f>
+        <f>'balance_raw_10290511'!$C$38</f>
         <v/>
       </c>
       <c r="D60" s="5">
-        <f>'balance_raw_10290511'!$D$39</f>
+        <f>'balance_raw_10290511'!$D$38</f>
         <v/>
       </c>
       <c r="E60" s="5">
-        <f>'balance_raw_10290511'!$E$39</f>
+        <f>'balance_raw_10290511'!$E$38</f>
         <v/>
       </c>
       <c r="F60" s="5">
-        <f>'balance_raw_10290511'!$F$39</f>
+        <f>'balance_raw_10290511'!$F$38</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3331,27 +3335,27 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B61" s="11">
-        <f>'balance_raw_10290511'!$B$40</f>
+        <f>'balance_raw_10290511'!$B$39</f>
         <v/>
       </c>
       <c r="C61" s="11">
-        <f>'balance_raw_10290511'!$C$40</f>
+        <f>'balance_raw_10290511'!$C$39</f>
         <v/>
       </c>
       <c r="D61" s="11">
-        <f>'balance_raw_10290511'!$D$40</f>
+        <f>'balance_raw_10290511'!$D$39</f>
         <v/>
       </c>
       <c r="E61" s="11">
-        <f>'balance_raw_10290511'!$E$40</f>
+        <f>'balance_raw_10290511'!$E$39</f>
         <v/>
       </c>
       <c r="F61" s="11">
-        <f>'balance_raw_10290511'!$F$40</f>
+        <f>'balance_raw_10290511'!$F$39</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3379,27 +3383,27 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B62" s="5">
-        <f>'balance_raw_10290511'!$B$41</f>
+        <f>'balance_raw_10290511'!$B$40</f>
         <v/>
       </c>
       <c r="C62" s="5">
-        <f>'balance_raw_10290511'!$C$41</f>
+        <f>'balance_raw_10290511'!$C$40</f>
         <v/>
       </c>
       <c r="D62" s="5">
-        <f>'balance_raw_10290511'!$D$41</f>
+        <f>'balance_raw_10290511'!$D$40</f>
         <v/>
       </c>
       <c r="E62" s="5">
-        <f>'balance_raw_10290511'!$E$41</f>
+        <f>'balance_raw_10290511'!$E$40</f>
         <v/>
       </c>
       <c r="F62" s="5">
-        <f>'balance_raw_10290511'!$F$41</f>
+        <f>'balance_raw_10290511'!$F$40</f>
         <v/>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3427,27 +3431,27 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B63" s="11">
-        <f>'balance_raw_10290511'!$B$42</f>
+        <f>'balance_raw_10290511'!$B$41</f>
         <v/>
       </c>
       <c r="C63" s="11">
-        <f>'balance_raw_10290511'!$C$42</f>
+        <f>'balance_raw_10290511'!$C$41</f>
         <v/>
       </c>
       <c r="D63" s="11">
-        <f>'balance_raw_10290511'!$D$42</f>
+        <f>'balance_raw_10290511'!$D$41</f>
         <v/>
       </c>
       <c r="E63" s="11">
-        <f>'balance_raw_10290511'!$E$42</f>
+        <f>'balance_raw_10290511'!$E$41</f>
         <v/>
       </c>
       <c r="F63" s="11">
-        <f>'balance_raw_10290511'!$F$42</f>
+        <f>'balance_raw_10290511'!$F$41</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3475,27 +3479,27 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B64" s="5">
-        <f>'balance_raw_10290511'!$B$43</f>
+        <f>'balance_raw_10290511'!$B$42</f>
         <v/>
       </c>
       <c r="C64" s="5">
-        <f>'balance_raw_10290511'!$C$43</f>
+        <f>'balance_raw_10290511'!$C$42</f>
         <v/>
       </c>
       <c r="D64" s="5">
-        <f>'balance_raw_10290511'!$D$43</f>
+        <f>'balance_raw_10290511'!$D$42</f>
         <v/>
       </c>
       <c r="E64" s="5">
-        <f>'balance_raw_10290511'!$E$43</f>
+        <f>'balance_raw_10290511'!$E$42</f>
         <v/>
       </c>
       <c r="F64" s="5">
-        <f>'balance_raw_10290511'!$F$43</f>
+        <f>'balance_raw_10290511'!$F$42</f>
         <v/>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3523,27 +3527,27 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B65" s="11">
-        <f>'balance_raw_10290511'!$B$44</f>
+        <f>'balance_raw_10290511'!$B$43</f>
         <v/>
       </c>
       <c r="C65" s="11">
-        <f>'balance_raw_10290511'!$C$44</f>
+        <f>'balance_raw_10290511'!$C$43</f>
         <v/>
       </c>
       <c r="D65" s="11">
-        <f>'balance_raw_10290511'!$D$44</f>
+        <f>'balance_raw_10290511'!$D$43</f>
         <v/>
       </c>
       <c r="E65" s="11">
-        <f>'balance_raw_10290511'!$E$44</f>
+        <f>'balance_raw_10290511'!$E$43</f>
         <v/>
       </c>
       <c r="F65" s="11">
-        <f>'balance_raw_10290511'!$F$44</f>
+        <f>'balance_raw_10290511'!$F$43</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3571,27 +3575,27 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B66" s="5">
-        <f>'balance_raw_10290511'!$B$45</f>
+        <f>'balance_raw_10290511'!$B$44</f>
         <v/>
       </c>
       <c r="C66" s="5">
-        <f>'balance_raw_10290511'!$C$45</f>
+        <f>'balance_raw_10290511'!$C$44</f>
         <v/>
       </c>
       <c r="D66" s="5">
-        <f>'balance_raw_10290511'!$D$45</f>
+        <f>'balance_raw_10290511'!$D$44</f>
         <v/>
       </c>
       <c r="E66" s="5">
-        <f>'balance_raw_10290511'!$E$45</f>
+        <f>'balance_raw_10290511'!$E$44</f>
         <v/>
       </c>
       <c r="F66" s="5">
-        <f>'balance_raw_10290511'!$F$45</f>
+        <f>'balance_raw_10290511'!$F$44</f>
         <v/>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3619,27 +3623,27 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B67" s="11">
-        <f>'balance_raw_10290511'!$B$46</f>
+        <f>'balance_raw_10290511'!$B$45</f>
         <v/>
       </c>
       <c r="C67" s="11">
-        <f>'balance_raw_10290511'!$C$46</f>
+        <f>'balance_raw_10290511'!$C$45</f>
         <v/>
       </c>
       <c r="D67" s="11">
-        <f>'balance_raw_10290511'!$D$46</f>
+        <f>'balance_raw_10290511'!$D$45</f>
         <v/>
       </c>
       <c r="E67" s="11">
-        <f>'balance_raw_10290511'!$E$46</f>
+        <f>'balance_raw_10290511'!$E$45</f>
         <v/>
       </c>
       <c r="F67" s="11">
-        <f>'balance_raw_10290511'!$F$46</f>
+        <f>'balance_raw_10290511'!$F$45</f>
         <v/>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3667,27 +3671,27 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B68" s="5">
-        <f>'balance_raw_10290511'!$B$47</f>
+        <f>'balance_raw_10290511'!$B$46</f>
         <v/>
       </c>
       <c r="C68" s="5">
-        <f>'balance_raw_10290511'!$C$47</f>
+        <f>'balance_raw_10290511'!$C$46</f>
         <v/>
       </c>
       <c r="D68" s="5">
-        <f>'balance_raw_10290511'!$D$47</f>
+        <f>'balance_raw_10290511'!$D$46</f>
         <v/>
       </c>
       <c r="E68" s="5">
-        <f>'balance_raw_10290511'!$E$47</f>
+        <f>'balance_raw_10290511'!$E$46</f>
         <v/>
       </c>
       <c r="F68" s="5">
-        <f>'balance_raw_10290511'!$F$47</f>
+        <f>'balance_raw_10290511'!$F$46</f>
         <v/>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3715,27 +3719,27 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="11">
-        <f>'balance_raw_10290511'!$B$48</f>
+        <f>'balance_raw_10290511'!$B$47</f>
         <v/>
       </c>
       <c r="C69" s="11">
-        <f>'balance_raw_10290511'!$C$48</f>
+        <f>'balance_raw_10290511'!$C$47</f>
         <v/>
       </c>
       <c r="D69" s="11">
-        <f>'balance_raw_10290511'!$D$48</f>
+        <f>'balance_raw_10290511'!$D$47</f>
         <v/>
       </c>
       <c r="E69" s="11">
-        <f>'balance_raw_10290511'!$E$48</f>
+        <f>'balance_raw_10290511'!$E$47</f>
         <v/>
       </c>
       <c r="F69" s="11">
-        <f>'balance_raw_10290511'!$F$48</f>
+        <f>'balance_raw_10290511'!$F$47</f>
         <v/>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3761,49 +3765,49 @@
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B70" s="8">
-        <f>'balance_raw_10290511'!$B$49</f>
-        <v/>
-      </c>
-      <c r="C70" s="8">
-        <f>'balance_raw_10290511'!$C$49</f>
-        <v/>
-      </c>
-      <c r="D70" s="8">
-        <f>'balance_raw_10290511'!$D$49</f>
-        <v/>
-      </c>
-      <c r="E70" s="8">
-        <f>'balance_raw_10290511'!$E$49</f>
-        <v/>
-      </c>
-      <c r="F70" s="8">
-        <f>'balance_raw_10290511'!$F$49</f>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B70" s="5">
+        <f>'balance_raw_10290511'!$B$48</f>
+        <v/>
+      </c>
+      <c r="C70" s="5">
+        <f>'balance_raw_10290511'!$C$48</f>
+        <v/>
+      </c>
+      <c r="D70" s="5">
+        <f>'balance_raw_10290511'!$D$48</f>
+        <v/>
+      </c>
+      <c r="E70" s="5">
+        <f>'balance_raw_10290511'!$E$48</f>
+        <v/>
+      </c>
+      <c r="F70" s="5">
+        <f>'balance_raw_10290511'!$F$48</f>
         <v/>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" s="9">
+      <c r="H70" s="6">
         <f>IFERROR(B70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="I70" s="9">
+      <c r="I70" s="6">
         <f>IFERROR(C70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="J70" s="9">
+      <c r="J70" s="6">
         <f>IFERROR(D70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="K70" s="9">
+      <c r="K70" s="6">
         <f>IFERROR(E70/$B$70*100,"")</f>
         <v/>
       </c>
-      <c r="L70" s="9">
+      <c r="L70" s="6">
         <f>IFERROR(F70/$B$70*100,"")</f>
         <v/>
       </c>
@@ -3811,27 +3815,27 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B71" s="8">
-        <f>'balance_raw_10290511'!$B$50</f>
+        <f>'balance_raw_10290511'!$B$49</f>
         <v/>
       </c>
       <c r="C71" s="8">
-        <f>'balance_raw_10290511'!$C$50</f>
+        <f>'balance_raw_10290511'!$C$49</f>
         <v/>
       </c>
       <c r="D71" s="8">
-        <f>'balance_raw_10290511'!$D$50</f>
+        <f>'balance_raw_10290511'!$D$49</f>
         <v/>
       </c>
       <c r="E71" s="8">
-        <f>'balance_raw_10290511'!$E$50</f>
+        <f>'balance_raw_10290511'!$E$49</f>
         <v/>
       </c>
       <c r="F71" s="8">
-        <f>'balance_raw_10290511'!$F$50</f>
+        <f>'balance_raw_10290511'!$F$49</f>
         <v/>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3859,27 +3863,27 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Passiver</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B72" s="8">
-        <f>'balance_raw_10290511'!$B$51</f>
+        <f>'balance_raw_10290511'!$B$50</f>
         <v/>
       </c>
       <c r="C72" s="8">
-        <f>'balance_raw_10290511'!$C$51</f>
+        <f>'balance_raw_10290511'!$C$50</f>
         <v/>
       </c>
       <c r="D72" s="8">
-        <f>'balance_raw_10290511'!$D$51</f>
+        <f>'balance_raw_10290511'!$D$50</f>
         <v/>
       </c>
       <c r="E72" s="8">
-        <f>'balance_raw_10290511'!$E$51</f>
+        <f>'balance_raw_10290511'!$E$50</f>
         <v/>
       </c>
       <c r="F72" s="8">
-        <f>'balance_raw_10290511'!$F$51</f>
+        <f>'balance_raw_10290511'!$F$50</f>
         <v/>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3904,80 +3908,80 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B73" s="8">
+        <f>'balance_raw_10290511'!$B$51</f>
+        <v/>
+      </c>
+      <c r="C73" s="8">
+        <f>'balance_raw_10290511'!$C$51</f>
+        <v/>
+      </c>
+      <c r="D73" s="8">
+        <f>'balance_raw_10290511'!$D$51</f>
+        <v/>
+      </c>
+      <c r="E73" s="8">
+        <f>'balance_raw_10290511'!$E$51</f>
+        <v/>
+      </c>
+      <c r="F73" s="8">
+        <f>'balance_raw_10290511'!$F$51</f>
+        <v/>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="9">
+        <f>IFERROR(B73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="9">
+        <f>IFERROR(C73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="9">
+        <f>IFERROR(D73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="K73" s="9">
+        <f>IFERROR(E73/$B$73*100,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="9">
+        <f>IFERROR(F73/$B$73*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B75" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C75" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D75" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="E75" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F75" s="3" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B75" s="11">
-        <f>'res_raw_10290511'!$B$17</f>
-        <v/>
-      </c>
-      <c r="C75" s="11">
-        <f>'res_raw_10290511'!$C$17</f>
-        <v/>
-      </c>
-      <c r="D75" s="11">
-        <f>'res_raw_10290511'!$D$17</f>
-        <v/>
-      </c>
-      <c r="E75" s="11">
-        <f>'res_raw_10290511'!$E$17</f>
-        <v/>
-      </c>
-      <c r="F75" s="11">
-        <f>'res_raw_10290511'!$F$17</f>
-        <v/>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="12">
-        <f>IFERROR(B75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="I75" s="12">
-        <f>IFERROR(C75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="12">
-        <f>IFERROR(D75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="K75" s="12">
-        <f>IFERROR(E75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="L75" s="12">
-        <f>IFERROR(F75/$B$75*100,"")</f>
-        <v/>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Investering i materielle anlægsaktiver</t>
+          <t>Gns. antal medarbejdere</t>
         </is>
       </c>
       <c r="B76" s="5">
@@ -4022,327 +4026,375 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B77" s="11">
+        <f>'res_raw_10290511'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C77" s="11">
+        <f>'res_raw_10290511'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D77" s="11">
+        <f>'res_raw_10290511'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E77" s="11">
+        <f>'res_raw_10290511'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F77" s="11">
+        <f>'res_raw_10290511'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="12">
+        <f>IFERROR(B77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="12">
+        <f>IFERROR(C77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="12">
+        <f>IFERROR(D77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="12">
+        <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="12">
+        <f>IFERROR(F77/$B$77*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>NØGLETAL</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B79" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C79" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D79" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F79" s="3" t="n">
         <v>2025</v>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B79" s="13">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="13">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="13">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="13">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="13">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$46*100,"")</f>
-        <v/>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B80" s="14">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="14">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="14">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="14">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="14">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>IFERROR(($B$12+$B$14+$B$13)/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="13">
+        <f>IFERROR(($C$12+$C$14+$C$13)/$C$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="13">
+        <f>IFERROR(($D$12+$D$14+$D$13)/$D$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="13">
+        <f>IFERROR(($E$12+$E$14+$E$13)/$E$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="13">
+        <f>IFERROR(($F$12+$F$14+$F$13)/$F$47*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B81" s="13">
-        <f>IFERROR($B$4/$B$46,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="13">
-        <f>IFERROR($C$4/$C$46,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="13">
-        <f>IFERROR($D$4/$D$46,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="13">
-        <f>IFERROR($E$4/$E$46,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="13">
-        <f>IFERROR($F$4/$F$46,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B81" s="14">
+        <f>IFERROR(($B$12+$B$14+$B$13)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="14">
+        <f>IFERROR(($C$12+$C$14+$C$13)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="14">
+        <f>IFERROR(($D$12+$D$14+$D$13)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>IFERROR(($E$12+$E$14+$E$13)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="14">
+        <f>IFERROR(($F$12+$F$14+$F$13)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B82" s="14">
-        <f>IFERROR($B$16/$B$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="14">
-        <f>IFERROR($C$16/$C$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="14">
-        <f>IFERROR($D$16/$D$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="14">
-        <f>IFERROR($E$16/$E$55*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="14">
-        <f>IFERROR($F$16/$F$55*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B82" s="13">
+        <f>IFERROR($B$4/$B$47,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="13">
+        <f>IFERROR($C$4/$C$47,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="13">
+        <f>IFERROR($D$4/$D$47,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="13">
+        <f>IFERROR($E$4/$E$47,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="13">
+        <f>IFERROR($F$4/$F$47,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B83" s="13">
-        <f>IFERROR($B$14/($B$72-$B$55)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="13">
-        <f>IFERROR($C$14/($C$72-$C$55)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="13">
-        <f>IFERROR($D$14/($D$72-$D$55)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="13">
-        <f>IFERROR($E$14/($E$72-$E$55)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="13">
-        <f>IFERROR($F$14/($F$72-$F$55)*100,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B83" s="14">
+        <f>IFERROR($B$17/$B$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="14">
+        <f>IFERROR($C$17/$C$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IFERROR($D$17/$D$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IFERROR($E$17/$E$56*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="14">
+        <f>IFERROR($F$17/$F$56*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B84" s="14">
-        <f>IFERROR($B$55/$B$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="14">
-        <f>IFERROR($C$55/$C$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="14">
-        <f>IFERROR($D$55/$D$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="14">
-        <f>IFERROR($E$55/$E$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="14">
-        <f>IFERROR($F$55/$F$46*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B84" s="13">
+        <f>IFERROR($B$15/($B$73-$B$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="13">
+        <f>IFERROR($C$15/($C$73-$C$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="13">
+        <f>IFERROR($D$15/($D$73-$D$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="13">
+        <f>IFERROR($E$15/($E$73-$E$56)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="13">
+        <f>IFERROR($F$15/($F$73-$F$56)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B85" s="13">
-        <f>IFERROR(($B$72-$B$55)/$B$55,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="13">
-        <f>IFERROR(($C$72-$C$55)/$C$55,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="13">
-        <f>IFERROR(($D$72-$D$55)/$D$55,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="13">
-        <f>IFERROR(($E$72-$E$55)/$E$55,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="13">
-        <f>IFERROR(($F$72-$F$55)/$F$55,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B85" s="14">
+        <f>IFERROR($B$56/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="14">
+        <f>IFERROR($C$56/$C$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="14">
+        <f>IFERROR($D$56/$D$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IFERROR($E$56/$E$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="14">
+        <f>IFERROR($F$56/$F$47*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B86" s="14">
-        <f>IFERROR($B$45/$B$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="14">
-        <f>IFERROR($C$45/$C$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="14">
-        <f>IFERROR($D$45/$D$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="14">
-        <f>IFERROR($E$45/$E$70*100,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="14">
-        <f>IFERROR($F$45/$F$70*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B86" s="13">
+        <f>IFERROR(($B$73-$B$56)/$B$56,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="13">
+        <f>IFERROR(($C$73-$C$56)/$C$56,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="13">
+        <f>IFERROR(($D$73-$D$56)/$D$56,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="13">
+        <f>IFERROR(($E$73-$E$56)/$E$56,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="13">
+        <f>IFERROR(($F$73-$F$56)/$F$56,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B87" s="13">
-        <f>IFERROR(B79-B83,"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="13">
-        <f>IFERROR(C79-C83,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="13">
-        <f>IFERROR(D79-D83,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="13">
-        <f>IFERROR(E79-E83,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="13">
-        <f>IFERROR(F79-F83,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B87" s="14">
+        <f>IFERROR($B$46/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="14">
+        <f>IFERROR($C$46/$C$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="14">
+        <f>IFERROR($D$46/$D$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>IFERROR($E$46/$E$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="14">
+        <f>IFERROR($F$46/$F$71*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B88" s="14">
-        <f>IFERROR(($B$72-$B$55)/$B$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="14">
-        <f>IFERROR(($C$72-$C$55)/$C$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="14">
-        <f>IFERROR(($D$72-$D$55)/$D$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="14">
-        <f>IFERROR(($E$72-$E$55)/$E$46*100,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="14">
-        <f>IFERROR(($F$72-$F$55)/$F$46*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B88" s="13">
+        <f>IFERROR(B80-B84,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="13">
+        <f>IFERROR(C80-C84,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="13">
+        <f>IFERROR(D80-D84,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="13">
+        <f>IFERROR(E80-E84,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="13">
+        <f>IFERROR(F80-F84,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B89" s="14">
+        <f>IFERROR(($B$73-$B$56)/$B$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="14">
+        <f>IFERROR(($C$73-$C$56)/$C$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="14">
+        <f>IFERROR(($D$73-$D$56)/$D$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="14">
+        <f>IFERROR(($E$73-$E$56)/$E$47*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="14">
+        <f>IFERROR(($F$73-$F$56)/$F$47*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B89" s="13">
-        <f>IFERROR($B$30/($B$55+$B$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="13">
-        <f>IFERROR($C$30/($C$55+$C$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="13">
-        <f>IFERROR($D$30/($D$55+$D$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="13">
-        <f>IFERROR($E$30/($E$55+$E$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="13">
-        <f>IFERROR($F$30/($F$55+$F$58)*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
+      <c r="B90" s="13">
+        <f>IFERROR($B$31/($B$56+$B$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="13">
+        <f>IFERROR($C$31/($C$56+$C$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="13">
+        <f>IFERROR($D$31/($D$56+$D$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="13">
+        <f>IFERROR($E$31/($E$56+$E$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="13">
+        <f>IFERROR($F$31/($F$56+$F$59)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
         <is>
           <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
         </is>
@@ -4359,7 +4411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4461,298 +4513,310 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomkostninger</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>93239</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>100273</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>99427</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>97706</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>96718</v>
-      </c>
+          <t>Udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>Administrationsomkostninger</t>
+          <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>24931</v>
+        <v>93239</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>18919</v>
+        <v>100273</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>21045</v>
+        <v>99427</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>22410</v>
+        <v>97706</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>21440</v>
+        <v>96718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>Andre driftsindtægter</t>
+          <t>Administrationsomkostninger</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>1760</v>
+        <v>24931</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>1265</v>
+        <v>18919</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1404</v>
+        <v>21045</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1742</v>
+        <v>22410</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>3096</v>
+        <v>21440</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
+          <t>Andre driftsindtægter</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>1760</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>1742</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B9" s="16" t="n">
         <v>5887</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C9" s="16" t="n">
         <v>728</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D9" s="16" t="n">
         <v>1162</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E9" s="16" t="n">
         <v>1165</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F9" s="16" t="n">
         <v>3568</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B10" s="16" t="n">
         <v>102385</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C10" s="16" t="n">
         <v>171580</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D10" s="16" t="n">
         <v>198852</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E10" s="16" t="n">
         <v>217916</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F10" s="16" t="n">
         <v>247882</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Indtægter af kapitalandele, dattervirksomheder</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>3320</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>3680</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Finansielle indtægter</t>
+          <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>307</v>
+        <v>3500</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5087</v>
+        <v>3000</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>8878</v>
+        <v>3320</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>6306</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
+          <t>Finansielle indtægter</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>307</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>5087</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>8878</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>6306</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B13" s="16" t="n">
         <v>966</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C13" s="16" t="n">
         <v>241</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D13" s="16" t="n">
         <v>489</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E13" s="16" t="n">
         <v>338</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F13" s="16" t="n">
         <v>622</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle poster, netto</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>Finansielle poster, netto</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B15" s="16" t="n">
         <v>102440</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C15" s="16" t="n">
         <v>175146</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D15" s="16" t="n">
         <v>206450</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E15" s="16" t="n">
         <v>229776</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F15" s="16" t="n">
         <v>257246</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>22329</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C16" s="16" t="n">
         <v>37803</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D16" s="16" t="n">
         <v>44877</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E16" s="16" t="n">
         <v>49931</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F16" s="16" t="n">
         <v>56156</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B17" s="16" t="n">
         <v>80111</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C17" s="16" t="n">
         <v>137343</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D17" s="16" t="n">
         <v>161573</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E17" s="16" t="n">
         <v>179845</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F17" s="16" t="n">
         <v>201090</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>104</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>94</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B19" s="16" t="n">
         <v>52100</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C19" s="16" t="n">
         <v>26700</v>
       </c>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5757,7 +5821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5862,15 +5926,15 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>IF(COUNT('res_raw_10290511'!$F$2,'res_raw_10290511'!$F$3)=0,'res_raw_10290511'!$F$4,SUM(B5:B6))</f>
+        <f>IF(ABS((SUM(B5:B6))-'res_raw_10290511'!$F$4)&lt;=2,SUM(B5:B6),'res_raw_10290511'!$F$4)</f>
         <v/>
       </c>
       <c r="C7" s="27">
-        <f>IF(COUNT('res_raw_10290511'!$E$2,'res_raw_10290511'!$E$3)=0,'res_raw_10290511'!$E$4,SUM(C5:C6))</f>
+        <f>IF(ABS((SUM(C5:C6))-'res_raw_10290511'!$E$4)&lt;=2,SUM(C5:C6),'res_raw_10290511'!$E$4)</f>
         <v/>
       </c>
       <c r="D7" s="27">
-        <f>IF(COUNT('res_raw_10290511'!$D$2,'res_raw_10290511'!$D$3)=0,'res_raw_10290511'!$D$4,SUM(D5:D6))</f>
+        <f>IF(ABS((SUM(D5:D6))-'res_raw_10290511'!$D$4)&lt;=2,SUM(D5:D6),'res_raw_10290511'!$D$4)</f>
         <v/>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -5882,7 +5946,7 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomk.</t>
+          <t>Udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B8" s="24">
@@ -5899,14 +5963,14 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>fsa:DistributionCosts (vises negativt). Marketing, salg, distribution.</t>
+          <t>ifrs-full:ResearchAndDevelopmentExpense (vises negativt). Udviklingsomkostninger ført i resultatet (v15_21; B&amp;O m.fl.).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>Administrationsomkostninger mv.</t>
+          <t>Salgs- og distributionsomk.</t>
         </is>
       </c>
       <c r="B9" s="24">
@@ -5923,1020 +5987,1064 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>fsa:AdministrativeExpenses (vises negativt). Generel administration.</t>
+          <t>fsa:DistributionCosts (vises negativt). Marketing, salg, distribution.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>Andre driftsindtægter</t>
+          <t>Administrationsomkostninger mv.</t>
         </is>
       </c>
       <c r="B10" s="24">
-        <f>'res_raw_10290511'!$F$7</f>
+        <f>-'res_raw_10290511'!$F$7</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>'res_raw_10290511'!$E$7</f>
+        <f>-'res_raw_10290511'!$E$7</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>'res_raw_10290511'!$D$7</f>
+        <f>-'res_raw_10290511'!$D$7</f>
         <v/>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>fsa:OtherOperatingIncome. Sekundære driftsindtægter (huslejeindtægter, off. tilskud, avancer mv.).</t>
+          <t>fsa:AdministrativeExpenses (vises negativt). Generel administration.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>Andre driftsomkostninger</t>
+          <t>Andre driftsindtægter</t>
         </is>
       </c>
       <c r="B11" s="24">
-        <f>-'res_raw_10290511'!$F$8</f>
+        <f>'res_raw_10290511'!$F$8</f>
         <v/>
       </c>
       <c r="C11" s="24">
-        <f>-'res_raw_10290511'!$E$8</f>
+        <f>'res_raw_10290511'!$E$8</f>
         <v/>
       </c>
       <c r="D11" s="24">
-        <f>-'res_raw_10290511'!$D$8</f>
+        <f>'res_raw_10290511'!$D$8</f>
         <v/>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>fsa:OtherOperatingExpenses (vises negativt). Sekundære driftsomkostninger.</t>
+          <t>fsa:OtherOperatingIncome. Sekundære driftsindtægter (huslejeindtægter, off. tilskud, avancer mv.).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>Andre driftsomkostninger</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>-'res_raw_10290511'!$F$9</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>-'res_raw_10290511'!$E$9</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>-'res_raw_10290511'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>fsa:OtherOperatingExpenses (vises negativt). Sekundære driftsomkostninger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B12" s="27">
-        <f>SUM(B7:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="27">
-        <f>SUM(C7:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>SUM(D7:D11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>Beregnet: Bruttoresultat − Salgs/dist. − Administration + Andre driftsindt. − Andre driftsomk. EBIT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Finansielle indtægter mv.</t>
-        </is>
-      </c>
-      <c r="B13" s="24">
-        <f>N('res_raw_10290511'!$F$10)+N('res_raw_10290511'!$F$11)</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>N('res_raw_10290511'!$E$10)+N('res_raw_10290511'!$E$11)</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>N('res_raw_10290511'!$D$10)+N('res_raw_10290511'!$D$11)</f>
+      <c r="B13" s="30">
+        <f>IF(ABS((SUM(B7:B12))-'res_raw_10290511'!$F$10)&lt;=2,SUM(B7:B12),'res_raw_10290511'!$F$10)</f>
+        <v/>
+      </c>
+      <c r="C13" s="30">
+        <f>IF(ABS((SUM(C7:C12))-'res_raw_10290511'!$E$10)&lt;=2,SUM(C7:C12),'res_raw_10290511'!$E$10)</f>
+        <v/>
+      </c>
+      <c r="D13" s="30">
+        <f>IF(ABS((SUM(D7:D12))-'res_raw_10290511'!$D$10)&lt;=2,SUM(D7:D12),'res_raw_10290511'!$D$10)</f>
         <v/>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromSubsidiaries + fsa:OtherFinanceIncome.</t>
+          <t>Beregnet: Bruttoresultat − Udviklingsomk. − Salgs/dist. − Administration + Andre driftsindt. − Andre driftsomk. EBIT.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>Finansielle omkostninger mv.</t>
+          <t>Finansielle indtægter mv.</t>
         </is>
       </c>
       <c r="B14" s="24">
-        <f>-'res_raw_10290511'!$F$12</f>
+        <f>N('res_raw_10290511'!$F$11)+N('res_raw_10290511'!$F$12)</f>
         <v/>
       </c>
       <c r="C14" s="24">
-        <f>-'res_raw_10290511'!$E$12</f>
+        <f>N('res_raw_10290511'!$E$11)+N('res_raw_10290511'!$E$12)</f>
         <v/>
       </c>
       <c r="D14" s="24">
-        <f>-'res_raw_10290511'!$D$12</f>
+        <f>N('res_raw_10290511'!$D$11)+N('res_raw_10290511'!$D$12)</f>
         <v/>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>fsa:OtherFinanceExpenses (vises negativt). Renteomkostninger, kurstab.</t>
+          <t>fsa:IncomeFromSubsidiaries + fsa:OtherFinanceIncome.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
+          <t>Finansielle omkostninger mv.</t>
+        </is>
+      </c>
+      <c r="B15" s="27">
+        <f>-'res_raw_10290511'!$F$13</f>
+        <v/>
+      </c>
+      <c r="C15" s="27">
+        <f>-'res_raw_10290511'!$E$13</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>-'res_raw_10290511'!$D$13</f>
+        <v/>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>fsa:OtherFinanceExpenses (vises negativt). Renteomkostninger, kurstab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B15" s="27">
-        <f>SUM(B12:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="27">
-        <f>SUM(C12:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
-        <f>SUM(D12:D14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="B16" s="30">
+        <f>IF(ABS((SUM(B13:B15))-'res_raw_10290511'!$F$15)&lt;=2,SUM(B13:B15),'res_raw_10290511'!$F$15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="30">
+        <f>IF(ABS((SUM(C13:C15))-'res_raw_10290511'!$E$15)&lt;=2,SUM(C13:C15),'res_raw_10290511'!$E$15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="30">
+        <f>IF(ABS((SUM(D13:D15))-'res_raw_10290511'!$D$15)&lt;=2,SUM(D13:D15),'res_raw_10290511'!$D$15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Beregnet: EBIT + Fin. indtægter + Fin. omk. EBT.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-    </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Uddrag af balance</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B18" s="24">
-        <f>'balance_raw_10290511'!$F$11</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>'balance_raw_10290511'!$E$11</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>'balance_raw_10290511'!$D$11</f>
-        <v/>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentAssets. Materielle, immaterielle og finansielle anlægsaktiver.</t>
-        </is>
-      </c>
+      <c r="B18" s="22" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>'balance_raw_10290511'!$F$11</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>'balance_raw_10290511'!$E$11</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>'balance_raw_10290511'!$D$11</f>
+        <v/>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>fsa:NoncurrentAssets. Materielle, immaterielle og finansielle anlægsaktiver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B19" s="24">
+      <c r="B20" s="24">
         <f>'balance_raw_10290511'!$F$26</f>
         <v/>
       </c>
-      <c r="C19" s="24">
+      <c r="C20" s="24">
         <f>'balance_raw_10290511'!$E$26</f>
         <v/>
       </c>
-      <c r="D19" s="24">
+      <c r="D20" s="24">
         <f>'balance_raw_10290511'!$D$26</f>
         <v/>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>fsa:CurrentAssets. Varebeholdninger, tilgodehavender, likvider.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Aktiver i alt</t>
         </is>
       </c>
-      <c r="B20" s="27">
-        <f>SUM(B18:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="27">
-        <f>SUM(C18:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="27">
-        <f>SUM(D18:D19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="B21" s="27">
+        <f>SUM(B19:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="27">
+        <f>SUM(C19:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>SUM(D19:D20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Beregnet: Anlægsaktiver + Omsætningsaktiver. Bør matche fsa:Assets.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Egenkapital</t>
-        </is>
-      </c>
-      <c r="B22" s="24">
-        <f>'balance_raw_10290511'!$F$34</f>
-        <v/>
-      </c>
-      <c r="C22" s="24">
-        <f>'balance_raw_10290511'!$E$34</f>
-        <v/>
-      </c>
-      <c r="D22" s="24">
-        <f>'balance_raw_10290511'!$D$34</f>
-        <v/>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>fsa:Equity. Selskabskapital, overført resultat, reserver.</t>
-        </is>
-      </c>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
+          <t>Egenkapital</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>'balance_raw_10290511'!$F$34</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>'balance_raw_10290511'!$E$34</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>'balance_raw_10290511'!$D$34</f>
+        <v/>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>fsa:Equity. Selskabskapital, overført resultat, reserver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
           <t>Forpligtelser</t>
         </is>
       </c>
-      <c r="B23" s="24">
+      <c r="B24" s="24">
         <f>'balance_raw_10290511'!$F$51-'balance_raw_10290511'!$F$34</f>
         <v/>
       </c>
-      <c r="C23" s="24">
+      <c r="C24" s="24">
         <f>'balance_raw_10290511'!$E$51-'balance_raw_10290511'!$E$34</f>
         <v/>
       </c>
-      <c r="D23" s="24">
+      <c r="D24" s="24">
         <f>'balance_raw_10290511'!$D$51-'balance_raw_10290511'!$D$34</f>
         <v/>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>Beregnet: Passiver (fsa:LiabilitiesAndEquity) − Egenkapital. Hensættelser + kort- og langfristet gæld.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Passiver i alt</t>
         </is>
       </c>
-      <c r="B24" s="27">
-        <f>SUM(B22:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="27">
-        <f>SUM(C22:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>SUM(D22:D23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="B25" s="27">
+        <f>SUM(B23:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="27">
+        <f>SUM(C23:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>SUM(D23:D24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Beregnet: Egenkapital + Forpligtelser. Bør matche Aktiver i alt.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Udvalgte balanceposter</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B27" s="24">
-        <f>'balance_raw_10290511'!$F$15</f>
-        <v/>
-      </c>
-      <c r="C27" s="24">
-        <f>'balance_raw_10290511'!$E$15</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>'balance_raw_10290511'!$D$15</f>
-        <v/>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>fsa:Inventories (eller fsa:ManufacturedGoodsAndGoodsForResale hvis total mangler).</t>
-        </is>
-      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg</t>
+          <t>Varebeholdninger</t>
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_10290511'!$F$16</f>
+        <f>'balance_raw_10290511'!$F$15</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_10290511'!$E$16</f>
+        <f>'balance_raw_10290511'!$E$15</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_10290511'!$D$16</f>
+        <f>'balance_raw_10290511'!$D$15</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>fsa:ShorttermTradeReceivables. Kortfristede tilgodehavender fra kunder.</t>
+          <t>fsa:Inventories (eller fsa:ManufacturedGoodsAndGoodsForResale hvis total mangler).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
+          <t>Tilgodehavender fra salg</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>'balance_raw_10290511'!$F$16</f>
+        <v/>
+      </c>
+      <c r="C29" s="24">
+        <f>'balance_raw_10290511'!$E$16</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>'balance_raw_10290511'!$D$16</f>
+        <v/>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>fsa:ShorttermTradeReceivables. Kortfristede tilgodehavender fra kunder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B29" s="24">
+      <c r="B30" s="24">
         <f>'balance_raw_10290511'!$F$49</f>
         <v/>
       </c>
-      <c r="C29" s="24">
+      <c r="C30" s="24">
         <f>'balance_raw_10290511'!$E$49</f>
         <v/>
       </c>
-      <c r="D29" s="24">
+      <c r="D30" s="24">
         <f>'balance_raw_10290511'!$D$49</f>
         <v/>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F30" s="25" t="inlineStr">
         <is>
           <t>fsa:ShorttermLiabilitiesOtherThanProvisions. Gæld der forfalder inden for 1 år.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="F30" s="29" t="n"/>
-    </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="F31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Rentabilitet</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B32" s="30">
-        <f>IFERROR((B12+B13)/B20*100,"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="30">
-        <f>IFERROR((C12+C13)/C20*100,"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="30">
-        <f>IFERROR((D12+D13)/D20*100,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="29" t="n"/>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B33" s="30">
-        <f>IFERROR((B12+B13)/B5*100,"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="30">
-        <f>IFERROR((C12+C13)/C5*100,"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="30">
-        <f>IFERROR((D12+D13)/D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="29" t="n"/>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B33" s="32">
+        <f>IFERROR((B13+B14)/B21*100,"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>IFERROR((C13+C14)/C21*100,"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>IFERROR((D13+D14)/D21*100,"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="31" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B34" s="30">
-        <f>IFERROR(B5/B20,"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="30">
-        <f>IFERROR(C5/C20,"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="30">
-        <f>IFERROR(D5/D20,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="29" t="n"/>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B34" s="32">
+        <f>IFERROR((B13+B14)/B5*100,"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>IFERROR((C13+C14)/C5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>IFERROR((D13+D14)/D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="31" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B35" s="30">
-        <f>IFERROR(-B14*100/B23,"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="30">
-        <f>IFERROR(-C14*100/C23,"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="30">
-        <f>IFERROR(-D14*100/D23,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="29" t="n"/>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B35" s="32">
+        <f>IFERROR(B5/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="32">
+        <f>IFERROR(C5/C21,"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>IFERROR(D5/D21,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="31" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B36" s="30">
-        <f>IFERROR(B15/B22*100,"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="30">
-        <f>IFERROR(C15/C22*100,"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="30">
-        <f>IFERROR(D15/D22*100,"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="29" t="n"/>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B36" s="32">
+        <f>IFERROR(-B15*100/B24,"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>IFERROR(-C15*100/C24,"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>IFERROR(-D15*100/D24,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="31" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>IFERROR(B16/B23*100,"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>IFERROR(C16/C23*100,"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>IFERROR(D16/D23*100,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
           <t>Gearing, gange</t>
         </is>
       </c>
-      <c r="B37" s="30">
-        <f>IFERROR(B23/B22,"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="30">
-        <f>IFERROR(C23/C22,"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="30">
-        <f>IFERROR(D23/D22,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="29" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="n"/>
-      <c r="B38" s="29" t="n"/>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="29" t="n"/>
-      <c r="F38" s="29" t="n"/>
+      <c r="B38" s="32">
+        <f>IFERROR(B24/B23,"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>IFERROR(C24/C23,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>IFERROR(D24/D23,"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Nettoomsætning</t>
-        </is>
-      </c>
-      <c r="B40" s="31">
-        <f>IFERROR(B5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="31">
-        <f>IFERROR(C5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="31">
-        <f>IFERROR(D5/$D5*100,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="29" t="n"/>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Produktionsomkostninger</t>
-        </is>
-      </c>
-      <c r="B41" s="31">
-        <f>IFERROR(B6/$D6*100,"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="31">
-        <f>IFERROR(C6/$D6*100,"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="31">
-        <f>IFERROR(D6/$D6*100,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="29" t="n"/>
+          <t>Nettoomsætning</t>
+        </is>
+      </c>
+      <c r="B41" s="33">
+        <f>IFERROR(B5/$D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="33">
+        <f>IFERROR(C5/$D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="33">
+        <f>IFERROR(D5/$D5*100,"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="31" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>Salgs- og distributionsomk.</t>
-        </is>
-      </c>
-      <c r="B42" s="31">
-        <f>IFERROR(B8/$D8*100,"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="31">
-        <f>IFERROR(C8/$D8*100,"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="31">
-        <f>IFERROR(D8/$D8*100,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="29" t="n"/>
+          <t>Produktionsomkostninger</t>
+        </is>
+      </c>
+      <c r="B42" s="33">
+        <f>IFERROR(B6/$D6*100,"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="33">
+        <f>IFERROR(C6/$D6*100,"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="33">
+        <f>IFERROR(D6/$D6*100,"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="31" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>Administrationsomk.</t>
-        </is>
-      </c>
-      <c r="B43" s="31">
-        <f>IFERROR(B9/$D9*100,"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="31">
-        <f>IFERROR(C9/$D9*100,"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="31">
-        <f>IFERROR(D9/$D9*100,"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="29" t="n"/>
+          <t>Udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B43" s="33">
+        <f>IFERROR(B8/$D8*100,"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="33">
+        <f>IFERROR(C8/$D8*100,"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="33">
+        <f>IFERROR(D8/$D8*100,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="31" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
         <is>
+          <t>Salgs- og distributionsomk.</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>IFERROR(B9/$D9*100,"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="33">
+        <f>IFERROR(C9/$D9*100,"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="33">
+        <f>IFERROR(D9/$D9*100,"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Administrationsomk.</t>
+        </is>
+      </c>
+      <c r="B45" s="33">
+        <f>IFERROR(B10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="33">
+        <f>IFERROR(C10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="33">
+        <f>IFERROR(D10/$D10*100,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B44" s="31">
-        <f>IFERROR(B11/$D11*100,"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="31">
-        <f>IFERROR(C11/$D11*100,"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="31">
-        <f>IFERROR(D11/$D11*100,"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="29" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="29" t="n"/>
-      <c r="D45" s="29" t="n"/>
-      <c r="F45" s="29" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="B46" s="33">
+        <f>IFERROR(B12/$D12*100,"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="33">
+        <f>IFERROR(C12/$D12*100,"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="33">
+        <f>IFERROR(D12/$D12*100,"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="n"/>
+      <c r="B47" s="31" t="n"/>
+      <c r="C47" s="31" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="F47" s="31" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="F46" s="22" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Nettoomsætning</t>
-        </is>
-      </c>
-      <c r="B47" s="31">
-        <f>IFERROR(B5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="31">
-        <f>IFERROR(C5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="31">
-        <f>IFERROR(D5*100/$D5,"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="29" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B48" s="31">
-        <f>IFERROR(B18*100/$D18,"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="31">
-        <f>IFERROR(C18*100/$D18,"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="31">
-        <f>IFERROR(D18*100/$D18,"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="29" t="n"/>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B49" s="31">
-        <f>IFERROR(B27*100/$D27,"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="31">
-        <f>IFERROR(C27*100/$D27,"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="31">
-        <f>IFERROR(D27*100/$D27,"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="29" t="n"/>
+          <t>Nettoomsætning</t>
+        </is>
+      </c>
+      <c r="B49" s="33">
+        <f>IFERROR(B5*100/$D5,"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="33">
+        <f>IFERROR(C5*100/$D5,"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="33">
+        <f>IFERROR(D5*100/$D5,"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="31" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B50" s="33">
+        <f>IFERROR(B19*100/$D19,"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="33">
+        <f>IFERROR(C19*100/$D19,"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="33">
+        <f>IFERROR(D19*100/$D19,"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="31" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B51" s="33">
+        <f>IFERROR(B28*100/$D28,"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="33">
+        <f>IFERROR(C28*100/$D28,"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="33">
+        <f>IFERROR(D28*100/$D28,"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="31" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
           <t>Tilgodehavender fra salg</t>
         </is>
       </c>
-      <c r="B50" s="31">
-        <f>IFERROR(B28*100/$D28,"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="31">
-        <f>IFERROR(C28*100/$D28,"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="31">
-        <f>IFERROR(D28*100/$D28,"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="29" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="29" t="n"/>
-      <c r="C51" s="29" t="n"/>
-      <c r="D51" s="29" t="n"/>
-      <c r="F51" s="29" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="B52" s="33">
+        <f>IFERROR(B29*100/$D29,"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="33">
+        <f>IFERROR(C29*100/$D29,"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="33">
+        <f>IFERROR(D29*100/$D29,"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="31" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="31" t="n"/>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="F53" s="31" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>Soliditet og likviditet</t>
         </is>
       </c>
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="F52" s="22" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="23" t="inlineStr">
-        <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B53" s="30">
-        <f>IFERROR(B22*100/B20,"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="30">
-        <f>IFERROR(C22*100/C20,"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="30">
-        <f>IFERROR(D22*100/D20,"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="29" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B54" s="30">
-        <f>IFERROR(B23*100/B20,"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="30">
-        <f>IFERROR(C23*100/C20,"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="30">
-        <f>IFERROR(D23*100/D20,"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="29" t="n"/>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B55" s="32">
+        <f>IFERROR(B23*100/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="32">
+        <f>IFERROR(C23*100/C21,"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="32">
+        <f>IFERROR(D23*100/D21,"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="31" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B56" s="32">
+        <f>IFERROR(B24*100/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="32">
+        <f>IFERROR(C24*100/C21,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="32">
+        <f>IFERROR(D24*100/D21,"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="31" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
           <t>Likviditetsgrad, %</t>
         </is>
       </c>
-      <c r="B55" s="30">
-        <f>IFERROR(B19*100/B29,"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="30">
-        <f>IFERROR(C19*100/C29,"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="30">
-        <f>IFERROR(D19*100/D29,"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="29" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="29" t="n"/>
-      <c r="B56" s="29" t="n"/>
-      <c r="C56" s="29" t="n"/>
-      <c r="D56" s="29" t="n"/>
-      <c r="F56" s="29" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="B57" s="32">
+        <f>IFERROR(B20*100/B30,"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="32">
+        <f>IFERROR(C20*100/C30,"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="32">
+        <f>IFERROR(D20*100/D30,"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="31" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="31" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="31" t="n"/>
+      <c r="F58" s="31" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
-      <c r="B57" s="29" t="n"/>
-      <c r="C57" s="29" t="n"/>
-      <c r="D57" s="29" t="n"/>
-      <c r="F57" s="29" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="29" t="n"/>
-      <c r="B58" s="29" t="n"/>
-      <c r="C58" s="29" t="n"/>
-      <c r="D58" s="29" t="n"/>
-      <c r="F58" s="29" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="B59" s="31" t="n"/>
+      <c r="C59" s="31" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="F59" s="31" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="n"/>
+      <c r="B60" s="31" t="n"/>
+      <c r="C60" s="31" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="F60" s="31" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>Krydstjek mod rådata (tolerance: 1 t.kr.)</t>
         </is>
       </c>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>Aktiver i alt = fsa:Assets</t>
-        </is>
-      </c>
-      <c r="B60" s="29">
-        <f>IF('balance_raw_10290511'!$F$27="","—",IF(ABS(B20-'balance_raw_10290511'!$F$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_10290511'!$F$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C60" s="29">
-        <f>IF('balance_raw_10290511'!$E$27="","—",IF(ABS(C20-'balance_raw_10290511'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_10290511'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D60" s="29">
-        <f>IF('balance_raw_10290511'!$D$27="","—",IF(ABS(D20-'balance_raw_10290511'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_10290511'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>Verificerer at sum(Anlæg+Omsætning) matcher Assets-totalen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>Passiver i alt = fsa:LiabilitiesAndEquity</t>
-        </is>
-      </c>
-      <c r="B61" s="29">
-        <f>IF('balance_raw_10290511'!$F$51="","—",IF(ABS(B24-'balance_raw_10290511'!$F$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_10290511'!$F$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C61" s="29">
-        <f>IF('balance_raw_10290511'!$E$51="","—",IF(ABS(C24-'balance_raw_10290511'!$E$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_10290511'!$E$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D61" s="29">
-        <f>IF('balance_raw_10290511'!$D$51="","—",IF(ABS(D24-'balance_raw_10290511'!$D$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_10290511'!$D$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="F61" s="25" t="inlineStr">
-        <is>
-          <t>Verificerer at sum(EK+Forpligtelser) matcher Passiver-totalen.</t>
-        </is>
-      </c>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="F61" s="22" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="23" t="inlineStr">
         <is>
-          <t>Aktiver i alt = Passiver i alt</t>
-        </is>
-      </c>
-      <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
-        <v/>
-      </c>
-      <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
-        <v/>
-      </c>
-      <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+          <t>Aktiver i alt = fsa:Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="31">
+        <f>IF('balance_raw_10290511'!$F$27="","—",IF(ABS(B21-'balance_raw_10290511'!$F$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_10290511'!$F$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C62" s="31">
+        <f>IF('balance_raw_10290511'!$E$27="","—",IF(ABS(C21-'balance_raw_10290511'!$E$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_10290511'!$E$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D62" s="31">
+        <f>IF('balance_raw_10290511'!$D$27="","—",IF(ABS(D21-'balance_raw_10290511'!$D$27)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_10290511'!$D$27,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>Balance-identitet på arket selv. Skal altid være 0 differance.</t>
+          <t>Verificerer at sum(Anlæg+Omsætning) matcher Assets-totalen.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>Bruttoresultat (beregnet) = fsa:GrossResult</t>
-        </is>
-      </c>
-      <c r="B63" s="29">
-        <f>IF('res_raw_10290511'!$F$4="","—",IF(ABS(B7-'res_raw_10290511'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_10290511'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C63" s="29">
-        <f>IF('res_raw_10290511'!$E$4="","—",IF(ABS(C7-'res_raw_10290511'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_10290511'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D63" s="29">
-        <f>IF('res_raw_10290511'!$D$4="","—",IF(ABS(D7-'res_raw_10290511'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_10290511'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+          <t>Passiver i alt = fsa:LiabilitiesAndEquity</t>
+        </is>
+      </c>
+      <c r="B63" s="31">
+        <f>IF('balance_raw_10290511'!$F$51="","—",IF(ABS(B25-'balance_raw_10290511'!$F$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_10290511'!$F$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C63" s="31">
+        <f>IF('balance_raw_10290511'!$E$51="","—",IF(ABS(C25-'balance_raw_10290511'!$E$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_10290511'!$E$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D63" s="31">
+        <f>IF('balance_raw_10290511'!$D$51="","—",IF(ABS(D25-'balance_raw_10290511'!$D$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_10290511'!$D$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
         <is>
-          <t>Hvis Nettoomsætning eller omkostninger mangler, vil sumberegnet bruttoresultat afvige.</t>
+          <t>Verificerer at sum(EK+Forpligtelser) matcher Passiver-totalen.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>EBIT (beregnet) = fsa:ProfitLossFromOrdinaryOperatingActivities</t>
-        </is>
-      </c>
-      <c r="B64" s="29">
-        <f>IF('res_raw_10290511'!$F$9="","—",IF(ABS(B12-'res_raw_10290511'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_10290511'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C64" s="29">
-        <f>IF('res_raw_10290511'!$E$9="","—",IF(ABS(C12-'res_raw_10290511'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_10290511'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D64" s="29">
-        <f>IF('res_raw_10290511'!$D$9="","—",IF(ABS(D12-'res_raw_10290511'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_10290511'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+          <t>Aktiver i alt = Passiver i alt</t>
+        </is>
+      </c>
+      <c r="B64" s="31">
+        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <v/>
+      </c>
+      <c r="C64" s="31">
+        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <v/>
+      </c>
+      <c r="D64" s="31">
+        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
         <is>
-          <t>Verificerer at sumberegnet EBIT matcher det rapporterede.</t>
+          <t>Balance-identitet på arket selv. Skal altid være 0 differance.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
+          <t>Bruttoresultat (beregnet) = fsa:GrossResult</t>
+        </is>
+      </c>
+      <c r="B65" s="31">
+        <f>IF('res_raw_10290511'!$F$4="","—",IF(ABS(B7-'res_raw_10290511'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_10290511'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C65" s="31">
+        <f>IF('res_raw_10290511'!$E$4="","—",IF(ABS(C7-'res_raw_10290511'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_10290511'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>IF('res_raw_10290511'!$D$4="","—",IF(ABS(D7-'res_raw_10290511'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_10290511'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>Hvis Nettoomsætning eller omkostninger mangler, vil sumberegnet bruttoresultat afvige.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>EBIT (beregnet) = fsa:ProfitLossFromOrdinaryOperatingActivities</t>
+        </is>
+      </c>
+      <c r="B66" s="31">
+        <f>IF('res_raw_10290511'!$F$10="","—",IF(ABS(B13-'res_raw_10290511'!$F$10)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_10290511'!$F$10,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C66" s="31">
+        <f>IF('res_raw_10290511'!$E$10="","—",IF(ABS(C13-'res_raw_10290511'!$E$10)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_10290511'!$E$10,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D66" s="31">
+        <f>IF('res_raw_10290511'!$D$10="","—",IF(ABS(D13-'res_raw_10290511'!$D$10)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_10290511'!$D$10,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>Verificerer at sumberegnet EBIT matcher det rapporterede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
           <t>EBT (beregnet) = fsa:ProfitLossFromOrdinaryActivitiesBeforeTax</t>
         </is>
       </c>
-      <c r="B65" s="29">
-        <f>IF('res_raw_10290511'!$F$14="","—",IF(ABS(B15-'res_raw_10290511'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_10290511'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="C65" s="29">
-        <f>IF('res_raw_10290511'!$E$14="","—",IF(ABS(C15-'res_raw_10290511'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_10290511'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="D65" s="29">
-        <f>IF('res_raw_10290511'!$D$14="","—",IF(ABS(D15-'res_raw_10290511'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_10290511'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
-        <v/>
-      </c>
-      <c r="F65" s="25" t="inlineStr">
+      <c r="B67" s="31">
+        <f>IF('res_raw_10290511'!$F$15="","—",IF(ABS(B16-'res_raw_10290511'!$F$15)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_10290511'!$F$15,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="C67" s="31">
+        <f>IF('res_raw_10290511'!$E$15="","—",IF(ABS(C16-'res_raw_10290511'!$E$15)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_10290511'!$E$15,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="D67" s="31">
+        <f>IF('res_raw_10290511'!$D$15="","—",IF(ABS(D16-'res_raw_10290511'!$D$15)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_10290511'!$D$15,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <v/>
+      </c>
+      <c r="F67" s="25" t="inlineStr">
         <is>
           <t>Verificerer at sumberegnet resultat før skat matcher det rapporterede.</t>
         </is>
@@ -6971,7 +7079,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Linde Gas A/S (CVR 10290511) — Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
         </is>
@@ -7025,177 +7133,177 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Øvrige (ukendt)</t>
         </is>
       </c>
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>fsa:Dividend</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>fsa:Dividend</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="35" t="n">
+      <c r="F3" s="37" t="n">
         <v>75000</v>
       </c>
-      <c r="G3" s="35" t="n">
+      <c r="G3" s="37" t="n">
         <v>100000</v>
       </c>
-      <c r="H3" s="35" t="n">
+      <c r="H3" s="37" t="n">
         <v>130000</v>
       </c>
-      <c r="I3" s="36" t="inlineStr">
+      <c r="I3" s="38" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Øvrige (ukendt)</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="40" t="n">
         <v>2355</v>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="40" t="n">
         <v>2092</v>
       </c>
-      <c r="F4" s="38" t="n">
+      <c r="F4" s="40" t="n">
         <v>2185</v>
       </c>
-      <c r="G4" s="38" t="n">
+      <c r="G4" s="40" t="n">
         <v>1851</v>
       </c>
-      <c r="H4" s="38" t="n">
+      <c r="H4" s="40" t="n">
         <v>1829</v>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Øvrige (ukendt)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>fsa:ShorttermContractWorkInProgressLiabilities</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>fsa:ShorttermContractWorkInProgressLiabilities</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="37" t="n">
         <v>13512</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="37" t="n">
         <v>15530</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="37" t="n">
         <v>4186</v>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="G5" s="37" t="n">
         <v>12567</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="37" t="n">
         <v>29420</v>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="I5" s="38" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Øvrige (ukendt)</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="40" t="n">
         <v>755</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="40" t="n">
         <v>1558</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="40" t="n">
         <v>1831</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="40" t="n">
         <v>1508</v>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="H6" s="40" t="n">
         <v>2807</v>
       </c>
-      <c r="I6" s="39" t="inlineStr">
+      <c r="I6" s="41" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Øvrige (ukendt)</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n">
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="36" t="inlineStr">
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="37" t="n"/>
+      <c r="H7" s="37" t="n"/>
+      <c r="I7" s="38" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer_2/10290511_linde_gas_a_s.xlsx
+++ b/filer_2/10290511_linde_gas_a_s.xlsx
@@ -4710,9 +4710,15 @@
       <c r="C14" s="16" t="n">
         <v>3600</v>
       </c>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="D14" s="16" t="n">
+        <v>4598</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>8540</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>5684</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
